--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-021_channel-opportunity/evidence/final_outputs/REQ-24_channel-opportunity/REQ-24-D01_channel_opportunity.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-021_channel-opportunity/evidence/final_outputs/REQ-24_channel-opportunity/REQ-24-D01_channel_opportunity.xlsx
@@ -531,7 +531,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Window: rolling 90 days, data through 2026-08-04 (last complete day).</t>
+          <t>Window: rolling 90 days, data through 2026-08-10 (last complete day).</t>
         </is>
       </c>
     </row>
@@ -691,10 +691,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -768,20 +768,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>12BO28</t>
+          <t>PHHCF1BMRBM</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>28</v>
-      </c>
       <c r="E5" s="6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -797,20 +797,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>PHHCF1BMRBM</t>
+          <t>SPSDP2BM</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -826,20 +826,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SPSDP2BM</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320RE</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -855,20 +855,20 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320RE</t>
+          <t>LHC6E27WH</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -882,89 +882,89 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>12IP2015</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace winner</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Add Shopify promotion</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>LHSHE27YB</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>228</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>266</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Missing channel</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>12DE2P10A</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace winner</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Add Shopify promotion</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>LDMST64E278</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Missing channel</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>SPSDP2WH3PK</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Marketplace winner</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Add Shopify promotion</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BI-JJ</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Missing channel</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1000,20 +1000,20 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BI-JJ</t>
+          <t>12IP6715</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1022,27 +1022,27 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E278</t>
+          <t>LHSHE27GB</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -1087,20 +1087,20 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>12IP6715</t>
+          <t>PHUH0.5HETBM</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1109,27 +1109,27 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E278</t>
+          <t>COS93BM</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1145,20 +1145,20 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>LHSHE27YB</t>
+          <t>LDMG95E274</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1174,20 +1174,20 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>PHUH0.5HETBM</t>
+          <t>LHSHE27BA</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -1196,27 +1196,27 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>COS93BM</t>
+          <t>12IP6736</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -1232,20 +1232,20 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E274</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320GR-DE</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -1254,27 +1254,27 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>12IP6736</t>
+          <t>LDMG95E278</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -1319,20 +1319,20 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320GR-DE</t>
+          <t>24IP2048</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -1341,27 +1341,27 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>LHSHE27BA</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM-JJ</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -1370,27 +1370,27 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM</t>
+          <t>CCBKNWE7</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -1406,20 +1406,20 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE7</t>
+          <t>CRSF100BM</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -1435,20 +1435,20 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>24IP2048</t>
+          <t>LSMS320RE+RPR44WH</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -1457,27 +1457,27 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>12IP6780</t>
+          <t>12IP2024</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -1493,20 +1493,20 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM-JJ</t>
+          <t>LSMS320BI+RPR44WH</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="D30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
@@ -1515,27 +1515,27 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>LSMS320RE+RPR44WH</t>
+          <t>12IP67100</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>12IP2024</t>
+          <t>12IP6730</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>LSMS320BI+RPR44WH</t>
+          <t>LHTHE27BN</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="C33" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>53</v>
-      </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Missing channel</t>
@@ -1602,27 +1602,27 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>COI9BBM</t>
+          <t>12IP6780</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -1638,20 +1638,20 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>12IP6730</t>
+          <t>COI9BBM</t>
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -1667,20 +1667,20 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>12IP67100</t>
+          <t>COS92BM2PK</t>
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
@@ -1706,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -1725,20 +1725,20 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>COS92BM</t>
+          <t>COT9ABM</t>
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
@@ -1754,20 +1754,20 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>COS92BM2PK</t>
+          <t>12BO48</t>
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
@@ -1776,27 +1776,27 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>LHSHE27GB</t>
+          <t>12IP20100</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -1841,20 +1841,20 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>CL2TWH</t>
+          <t>HLHG120CH2PK</t>
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
@@ -1870,20 +1870,20 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27BN</t>
+          <t>12IP20120</t>
         </is>
       </c>
       <c r="B43" s="8" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -1899,20 +1899,20 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>12IP20120</t>
+          <t>LSCY290BG+RPR44WH</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="8" t="n">
-        <v>40</v>
-      </c>
       <c r="E44" s="8" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -1928,20 +1928,20 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>12BO48</t>
+          <t>CCBKNWE12</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -1957,20 +1957,20 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>HLHG120CH2PK</t>
+          <t>12IP20150</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -1979,14 +1979,14 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>12IP20100</t>
+          <t>COS92BM</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
@@ -1996,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -2015,20 +2015,20 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BG+RPR44WH</t>
+          <t>5IP2050</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -2044,20 +2044,20 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE12</t>
+          <t>CCBKNWE18</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -2073,20 +2073,20 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHRYWP1RBM</t>
+          <t>CL3TGL</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C50" s="8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
@@ -2095,27 +2095,27 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE36</t>
+          <t>24IP6710</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -2131,20 +2131,20 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>12IP20150</t>
+          <t>CCBKNWE36</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C52" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
@@ -2153,27 +2153,27 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>5IP2050</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320GY-DE</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C53" s="8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -2182,27 +2182,27 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>CL3TGL</t>
+          <t>LDMST64E274APK</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C54" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -2218,20 +2218,20 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>COT9ABM</t>
+          <t>12IP2040</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -2247,20 +2247,20 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE18</t>
+          <t>24IP20240</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C56" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
@@ -2276,20 +2276,20 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>24IP6710</t>
+          <t>CRSF100BM+PHRYWP1RBM</t>
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
@@ -2298,27 +2298,27 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>LDST185E274</t>
+          <t>12BO28</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -2334,20 +2334,20 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>LHC3E27WH</t>
+          <t>12IP2080</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
@@ -2356,14 +2356,14 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>12IP2080</t>
+          <t>CL2ROR</t>
         </is>
       </c>
       <c r="B60" s="8" t="n">
@@ -2373,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
@@ -2392,20 +2392,20 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>12IP2040</t>
+          <t>LDST185E274</t>
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C61" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" s="8" t="n">
         <v>32</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>33</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>CL2ROR</t>
+          <t>LHC3E27WH</t>
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E62" s="8" t="n">
         <v>32</v>
@@ -2443,27 +2443,27 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E274APK</t>
+          <t>PHUH2HETBM</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C63" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E64" s="8" t="n">
         <v>30</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>32</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
@@ -2508,20 +2508,20 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>PHUH2HETBM</t>
+          <t>5IP2010</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C65" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -2530,27 +2530,27 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>5IP2010</t>
+          <t>LDMT45E274</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C66" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
@@ -2559,27 +2559,27 @@
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>24IP20240</t>
+          <t>12IP67150</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
@@ -2605,10 +2605,10 @@
         <v>0</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>PHCH1BMRBM+LSCY290BG-TJ</t>
+          <t>LSSS300BG+RPR44WH</t>
         </is>
       </c>
       <c r="B69" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C69" s="8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D69" s="8" t="n">
         <v>0</v>
@@ -2646,27 +2646,27 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>CCGNNWE24</t>
+          <t>24IP20120</t>
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C70" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>CL3TLB</t>
+          <t>5IP20100</t>
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C71" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E71" s="8" t="n">
         <v>28</v>
@@ -2704,24 +2704,24 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>LDMT45E274</t>
+          <t>CL3TLB</t>
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C72" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E72" s="8" t="n">
         <v>28</v>
@@ -2733,24 +2733,24 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE25</t>
+          <t>PHCH1BMRBM+LSCY290BG-TJ</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E73" s="8" t="n">
         <v>28</v>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
@@ -2779,10 +2779,10 @@
         <v>0</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
@@ -2798,20 +2798,20 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>5IP20100</t>
+          <t>CCGNNWE36</t>
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C75" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
@@ -2827,20 +2827,20 @@
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320GY-DE</t>
+          <t>CRSF100BM+WSCH135BM+LSHH240BM</t>
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C76" s="8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -2849,24 +2849,24 @@
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>24IP20120</t>
+          <t>PHHT2PBRBM</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C77" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E77" s="8" t="n">
         <v>27</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>CCGNNWE48</t>
+          <t>WJBIP685BM2PK</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
@@ -2914,20 +2914,20 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>PHHT2PBRBM</t>
+          <t>CCGNNWE48</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C79" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -2936,27 +2936,27 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSCH135BM+LSHH240BM</t>
+          <t>CRFF500BM+PHCH1BMRBM3PK+LSCY210BG3PK-J</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="C80" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="D80" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
@@ -2965,24 +2965,24 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>12IP67200</t>
+          <t>LHTHE27CO</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C81" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E81" s="8" t="n">
         <v>26</v>
@@ -3001,17 +3001,17 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27CO</t>
+          <t>PHHCF1BMRYB</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E82" s="8" t="n">
         <v>26</v>
@@ -3023,27 +3023,27 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>PHHCF1BMRYB</t>
+          <t>CCBKNWE25</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C83" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -3088,17 +3088,17 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>12IP20480</t>
+          <t>LDMG80E274</t>
         </is>
       </c>
       <c r="B85" s="8" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C85" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E85" s="8" t="n">
         <v>25</v>
@@ -3117,20 +3117,20 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>WJBIP685BM2PK</t>
+          <t>12IP67200</t>
         </is>
       </c>
       <c r="B86" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C86" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
@@ -3139,27 +3139,27 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>CCBC7</t>
+          <t>COS93BM4PK</t>
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C87" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
@@ -3168,27 +3168,27 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>COS93BM4PK</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320WH-DE</t>
         </is>
       </c>
       <c r="B88" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>CCGNNWE36</t>
+          <t>12IP20180</t>
         </is>
       </c>
       <c r="B89" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C89" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
@@ -3226,27 +3226,27 @@
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>24IP67120</t>
+          <t>12IP20480</t>
         </is>
       </c>
       <c r="B90" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
@@ -3255,27 +3255,27 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>12IP67150</t>
+          <t>12IP20600</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="C91" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="8" t="n">
-        <v>8</v>
-      </c>
       <c r="E91" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
@@ -3291,20 +3291,20 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>5IP2030</t>
+          <t>24IP20400</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E92" s="8" t="n">
         <v>23</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>24</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93" s="8" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>20</v>
       </c>
       <c r="E93" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
@@ -3349,11 +3349,11 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>5IP2020</t>
+          <t>24IP67120</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" s="8" t="n">
         <v>0</v>
@@ -3362,7 +3362,7 @@
         <v>23</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
@@ -3371,24 +3371,24 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>WJBIP68T13BM2PK</t>
+          <t>CNP1000YB</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C95" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E95" s="8" t="n">
         <v>23</v>
@@ -3400,24 +3400,24 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE50</t>
+          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
         </is>
       </c>
       <c r="B96" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E96" s="8" t="n">
         <v>23</v>
@@ -3429,24 +3429,24 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>12IP20180</t>
+          <t>KNNT1- 74 B</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E97" s="8" t="n">
         <v>23</v>
@@ -3458,24 +3458,24 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>24IP2072</t>
+          <t>LSCY290WH+RPR44WH C</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C98" s="8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E98" s="8" t="n">
         <v>23</v>
@@ -3487,24 +3487,24 @@
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>WJB2</t>
+          <t>LSDO300BI2PK+RPR44WH2PK_DE</t>
         </is>
       </c>
       <c r="B99" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C99" s="8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E99" s="8" t="n">
         <v>23</v>
@@ -3516,24 +3516,24 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>CRFF500BM+PHCH1BMRBM3PK+LSCY210BG3PK-J</t>
+          <t>WJBIP68T13BM2PK</t>
         </is>
       </c>
       <c r="B100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="8" t="n">
         <v>23</v>
-      </c>
-      <c r="D100" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E100" s="8" t="n">
         <v>23</v>
@@ -3545,27 +3545,27 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>LHC2E27WH</t>
+          <t>COT9ABM6PK</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C101" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E101" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
@@ -3574,18 +3574,18 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>CNP1000YB</t>
+          <t>CRSF100BM+LHNSE27YB+LSHH240BM</t>
         </is>
       </c>
       <c r="B102" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C102" s="8" t="n">
         <v>0</v>
@@ -3594,7 +3594,7 @@
         <v>3</v>
       </c>
       <c r="E102" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
@@ -3610,20 +3610,20 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>LSCY290WH+RPR44WH C</t>
+          <t>LHC2E27WH</t>
         </is>
       </c>
       <c r="B103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E103" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
@@ -3632,27 +3632,27 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>LDMG80E274</t>
+          <t>LSCP150WH2PK+RPR44WH2PK</t>
         </is>
       </c>
       <c r="B104" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C104" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
@@ -3661,27 +3661,27 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>LSDO300BI2PK+RPR44WH2PK_DE</t>
+          <t>12IP20240</t>
         </is>
       </c>
       <c r="B105" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C105" s="8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
@@ -3690,14 +3690,14 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
+          <t>24IP20360</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
@@ -3707,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
@@ -3726,20 +3726,20 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>LSCY210BG+RPR44WH</t>
+          <t>5IP2020</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C107" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
@@ -3748,27 +3748,27 @@
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320WH-DE</t>
+          <t>CCGNNWE24</t>
         </is>
       </c>
       <c r="B108" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C108" s="8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
@@ -3777,27 +3777,27 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>24IP20400</t>
+          <t>CL2TGY</t>
         </is>
       </c>
       <c r="B109" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C109" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
@@ -3806,27 +3806,27 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>LSCP150WH2PK+RPR44WH2PK</t>
+          <t>CRSF100BM+WSLS155BM</t>
         </is>
       </c>
       <c r="B110" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C110" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D110" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E110" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
@@ -3835,27 +3835,27 @@
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>WJBIP686BM</t>
+          <t>LSFT220BB+RPR44WH A</t>
         </is>
       </c>
       <c r="B111" s="8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C111" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E111" s="8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
@@ -3864,24 +3864,24 @@
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>12IP20240</t>
+          <t>PHUH1HETBM</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E112" s="8" t="n">
         <v>21</v>
@@ -3900,17 +3900,17 @@
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E2742PK</t>
+          <t>WJBIP686BM</t>
         </is>
       </c>
       <c r="B113" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C113" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E113" s="8" t="n">
         <v>21</v>
@@ -3922,24 +3922,24 @@
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>12SIP67100</t>
+          <t>WSNWBM+LSCY290BM+LDMST64E274</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E114" s="8" t="n">
         <v>21</v>
@@ -3951,27 +3951,27 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E276</t>
+          <t>12SIP67100</t>
         </is>
       </c>
       <c r="B115" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C115" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E115" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
@@ -3987,20 +3987,20 @@
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>ENC3611</t>
+          <t>COI9BBM2PK</t>
         </is>
       </c>
       <c r="B116" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
@@ -4009,27 +4009,27 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>12IP20600</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320RE</t>
         </is>
       </c>
       <c r="B117" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C117" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E117" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
@@ -4038,27 +4038,27 @@
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>CL2TGY</t>
+          <t>CRSF100BM+PHDO1PBRBM+LSTM310BM</t>
         </is>
       </c>
       <c r="B118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
@@ -4067,27 +4067,27 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E2782PK</t>
+          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
         </is>
       </c>
       <c r="B119" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C119" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
@@ -4103,20 +4103,20 @@
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>LSFT220BB+RPR44WH A</t>
+          <t>CRSF100BM+PHRI1PBRBY+LSDO210BG_DE</t>
         </is>
       </c>
       <c r="B120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D120" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
@@ -4132,20 +4132,20 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>5IP20150</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290WH-JJ</t>
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C121" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
@@ -4154,28 +4154,28 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>12IP6720</t>
+          <t>CRSF100YE+WSCH135YE+LSDO210YE</t>
         </is>
       </c>
       <c r="B122" s="8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C122" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D122" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E122" s="8" t="n">
-        <v>21</v>
-      </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
           <t>Missing channel</t>
@@ -4183,27 +4183,27 @@
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27YB+LSHH240BM</t>
+          <t>LDMG95E2782PK</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C123" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E123" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
@@ -4219,20 +4219,20 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>PHUH1HETBM</t>
+          <t>LHTHE27GB</t>
         </is>
       </c>
       <c r="B124" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C124" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E124" s="8" t="n">
         <v>20</v>
-      </c>
-      <c r="C124" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>21</v>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>12IP20360</t>
+          <t>LSCY210BG3PK</t>
         </is>
       </c>
       <c r="B125" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E125" s="8" t="n">
         <v>20</v>
@@ -4270,27 +4270,27 @@
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27GB</t>
+          <t>12IP20360</t>
         </is>
       </c>
       <c r="B126" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C126" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E126" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
@@ -4299,27 +4299,27 @@
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>LSCY210BG3PK</t>
+          <t>12IP67120</t>
         </is>
       </c>
       <c r="B127" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D127" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E127" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
@@ -4328,24 +4328,24 @@
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
+          <t>CCBC7</t>
         </is>
       </c>
       <c r="B128" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C128" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E128" s="8" t="n">
         <v>19</v>
@@ -4364,17 +4364,17 @@
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>COI9BBM2PK</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320BI</t>
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C129" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E129" s="8" t="n">
         <v>19</v>
@@ -4386,21 +4386,21 @@
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>ENC9452</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
         </is>
       </c>
       <c r="B130" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="8" t="n">
         <v>19</v>
-      </c>
-      <c r="C130" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D130" s="8" t="n">
         <v>0</v>
@@ -4415,24 +4415,24 @@
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290WH-JJ</t>
+          <t>LDMST64E2742PK</t>
         </is>
       </c>
       <c r="B131" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" s="8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>19</v>
@@ -4444,24 +4444,24 @@
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>24IP20360</t>
+          <t>LDMST64E276</t>
         </is>
       </c>
       <c r="B132" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C132" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E132" s="8" t="n">
         <v>19</v>
@@ -4473,27 +4473,27 @@
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320RE</t>
+          <t>12IP67120OL2</t>
         </is>
       </c>
       <c r="B133" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C133" s="8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>LHSHE27WH</t>
+          <t>24IP2072</t>
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C134" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E134" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
@@ -4531,27 +4531,27 @@
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>12IP67120</t>
+          <t>24IP6730</t>
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C135" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E135" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
@@ -4560,24 +4560,24 @@
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>24IP6730</t>
+          <t>5IP20150</t>
         </is>
       </c>
       <c r="B136" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>18</v>
@@ -4596,17 +4596,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>12IP20300</t>
+          <t>CL3TBU</t>
         </is>
       </c>
       <c r="B137" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E137" s="8" t="n">
         <v>18</v>
@@ -4625,17 +4625,17 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>CRFF108YB+WSSS70YB+SCRN70YB</t>
+          <t>CRSF100YB+WSSS70YB+LSFT220BC</t>
         </is>
       </c>
       <c r="B138" s="8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C138" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>18</v>
@@ -4647,21 +4647,21 @@
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320OR</t>
+          <t>ENC3611</t>
         </is>
       </c>
       <c r="B139" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C139" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D139" s="8" t="n">
         <v>0</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>WLHSBMSQ10</t>
+          <t>ENC9452</t>
         </is>
       </c>
       <c r="B140" s="8" t="n">
@@ -4712,17 +4712,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>PHCT1BMRBM+PHBA1BMRBM+LSDO300BM</t>
+          <t>LSFT220WH+RPR44WH</t>
         </is>
       </c>
       <c r="B141" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C141" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E141" s="8" t="n">
         <v>18</v>
@@ -4734,24 +4734,24 @@
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27SN</t>
+          <t>LSMS320BI+RPR44WH D</t>
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C142" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E142" s="8" t="n">
         <v>18</v>
@@ -4763,24 +4763,24 @@
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>CL3TBU</t>
+          <t>PHCT1BMRBM+PHBA1BMRBM+LSDO300BM</t>
         </is>
       </c>
       <c r="B143" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C143" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E143" s="8" t="n">
         <v>18</v>
@@ -4792,24 +4792,24 @@
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>12IP67350</t>
+          <t>PLOTBM+LSFT220BM</t>
         </is>
       </c>
       <c r="B144" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C144" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E144" s="8" t="n">
         <v>18</v>
@@ -4821,21 +4821,21 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>LSMS320BI+RPR44WH D</t>
+          <t>WLHSBMSQ10</t>
         </is>
       </c>
       <c r="B145" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C145" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D145" s="8" t="n">
         <v>0</v>
@@ -4850,14 +4850,14 @@
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>5IP2025</t>
+          <t>24IP20200</t>
         </is>
       </c>
       <c r="B146" s="8" t="n">
@@ -4867,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E146" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
@@ -4886,20 +4886,20 @@
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>LSMS320GR+RPR44WH</t>
+          <t>CL2THE5PK</t>
         </is>
       </c>
       <c r="B147" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C147" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D147" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
@@ -4908,18 +4908,18 @@
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>12BO100</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM</t>
         </is>
       </c>
       <c r="B148" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148" s="8" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
         <v>15</v>
       </c>
       <c r="E148" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
@@ -4944,20 +4944,20 @@
     <row r="149">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>LSFT220WH+RPR44WH</t>
+          <t>LSCP150BA2PK+RPR44WH2PK-DE</t>
         </is>
       </c>
       <c r="B149" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C149" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E149" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
@@ -4966,27 +4966,27 @@
       </c>
       <c r="G149" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>24IP6780</t>
+          <t>12IP20300</t>
         </is>
       </c>
       <c r="B150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -4995,27 +4995,27 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>COT9ABM6PK</t>
+          <t>12IP67350</t>
         </is>
       </c>
       <c r="B151" s="8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C151" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E151" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
@@ -5024,27 +5024,27 @@
       </c>
       <c r="G151" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>LHC6E27WH</t>
+          <t>24IP6736</t>
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C152" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D152" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E152" s="8" t="n">
         <v>16</v>
-      </c>
-      <c r="E152" s="8" t="n">
-        <v>17</v>
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
@@ -5060,20 +5060,20 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM2PK - Nb</t>
+          <t>24IP6780</t>
         </is>
       </c>
       <c r="B153" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C153" s="8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F153" s="7" t="inlineStr">
         <is>
@@ -5082,18 +5082,18 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E2783PK</t>
+          <t>COS93BM5PK</t>
         </is>
       </c>
       <c r="B154" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154" s="8" t="n">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>16</v>
       </c>
       <c r="E154" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
@@ -5111,27 +5111,27 @@
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>CRSF100BM+PHHT1PBRBM2PK - Nb</t>
         </is>
       </c>
       <c r="B155" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C155" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D155" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
@@ -5140,27 +5140,27 @@
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>WSNWBM+LSCY290BM+LDMST64E274</t>
+          <t>CRSF100BM+PHMU1PBRGS+LSDO210BG+ICST64E27</t>
         </is>
       </c>
       <c r="B156" s="8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C156" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D156" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E156" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
@@ -5169,27 +5169,27 @@
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290OR-JJ</t>
         </is>
       </c>
       <c r="B157" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C157" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D157" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
@@ -5198,27 +5198,27 @@
       </c>
       <c r="G157" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>24IP20180</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320OR</t>
         </is>
       </c>
       <c r="B158" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C158" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D158" s="8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E158" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
@@ -5227,24 +5227,24 @@
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>CBSF100</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320YE-DE</t>
         </is>
       </c>
       <c r="B159" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C159" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D159" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E159" s="8" t="n">
         <v>16</v>
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="B160" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C160" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D160" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E160" s="8" t="n">
         <v>16</v>
@@ -5285,24 +5285,24 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>24IP6736</t>
+          <t>LHNSE27CO</t>
         </is>
       </c>
       <c r="B161" s="8" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C161" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D161" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E161" s="8" t="n">
         <v>16</v>
@@ -5314,24 +5314,24 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>COS93BM5PK</t>
+          <t>LHTHE27SN</t>
         </is>
       </c>
       <c r="B162" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C162" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D162" s="8" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E162" s="8" t="n">
         <v>16</v>
@@ -5343,24 +5343,24 @@
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>LDMG80E2743PK</t>
+          <t>WCB3BM2PK+RPR44WH2PK j</t>
         </is>
       </c>
       <c r="B163" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C163" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D163" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E163" s="8" t="n">
         <v>16</v>
@@ -5372,24 +5372,24 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHDO1PBRBM+LSTM310BM</t>
+          <t>WCB7WH+RPR44WH</t>
         </is>
       </c>
       <c r="B164" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C164" s="8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D164" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E164" s="8" t="n">
         <v>16</v>
@@ -5401,24 +5401,24 @@
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>LSCP150BA2PK+RPR44WH2PK-DE</t>
+          <t>WJB2</t>
         </is>
       </c>
       <c r="B165" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="8" t="n">
         <v>16</v>
-      </c>
-      <c r="D165" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E165" s="8" t="n">
         <v>16</v>
@@ -5430,27 +5430,27 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHMU1PBRGS+LSDO210BG+ICST64E27</t>
+          <t>12BO100</t>
         </is>
       </c>
       <c r="B166" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C166" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D166" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E166" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
@@ -5459,27 +5459,27 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>WCB3BM2PK+RPR44WH2PK j</t>
+          <t>24IP20180</t>
         </is>
       </c>
       <c r="B167" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C167" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D167" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
@@ -5488,27 +5488,27 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSHR135BM+LSFT220BM</t>
+          <t>24IP6760</t>
         </is>
       </c>
       <c r="B168" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C168" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D168" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E168" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
@@ -5517,27 +5517,27 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>CL2THE5PK</t>
+          <t>5IP2025</t>
         </is>
       </c>
       <c r="B169" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C169" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D169" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
@@ -5546,27 +5546,27 @@
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>LHC5E27WH</t>
+          <t>CRFF108YB+WSSS70YB+SCRN70YB</t>
         </is>
       </c>
       <c r="B170" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C170" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D170" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E170" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
@@ -5582,20 +5582,20 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSHM400HE</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BU-JJ</t>
         </is>
       </c>
       <c r="B171" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C171" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D171" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E171" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
@@ -5604,27 +5604,27 @@
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>COS93BM3PK</t>
+          <t>CRSF100BM+WSHR135BM+LSFT220BM</t>
         </is>
       </c>
       <c r="B172" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C172" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D172" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E172" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
@@ -5633,28 +5633,28 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320BI</t>
+          <t>CRSF100YB+PHRI1PBRYB+LSDO300YB+ICST64E27</t>
         </is>
       </c>
       <c r="B173" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="D173" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" s="8" t="n">
-        <v>16</v>
-      </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
           <t>Missing channel</t>
@@ -5662,24 +5662,24 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E2745PK</t>
+          <t>CRSF108BM+WSST70BM</t>
         </is>
       </c>
       <c r="B174" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C174" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D174" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E174" s="8" t="n">
         <v>15</v>
@@ -5698,17 +5698,17 @@
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+PHRI1PBRYB+LSDO300YB+ICST64E27</t>
+          <t>LDMST64E2745PK</t>
         </is>
       </c>
       <c r="B175" s="8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C175" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D175" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E175" s="8" t="n">
         <v>15</v>
@@ -5720,24 +5720,24 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>PHSH1PBRYB</t>
+          <t>LHC5E27WH</t>
         </is>
       </c>
       <c r="B176" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C176" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D176" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E176" s="8" t="n">
         <v>15</v>
@@ -5756,17 +5756,17 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>CRSF108BM+WSST70BM</t>
+          <t>LHC5E27WH3PK</t>
         </is>
       </c>
       <c r="B177" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C177" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D177" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E177" s="8" t="n">
         <v>15</v>
@@ -5778,21 +5778,21 @@
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YE+WSCH135YE+LSDO210YE</t>
+          <t>LSHQ180BG2PK_DE</t>
         </is>
       </c>
       <c r="B178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" s="8" t="n">
         <v>15</v>
-      </c>
-      <c r="C178" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D178" s="8" t="n">
         <v>0</v>
@@ -5807,24 +5807,24 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>ENC7499</t>
+          <t>PHSH1PBRCO</t>
         </is>
       </c>
       <c r="B179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" s="8" t="n">
         <v>15</v>
-      </c>
-      <c r="C179" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D179" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E179" s="8" t="n">
         <v>15</v>
@@ -5836,27 +5836,27 @@
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>LSHQ180BG2PK_DE</t>
+          <t>12ASIP20300</t>
         </is>
       </c>
       <c r="B180" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C180" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D180" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
@@ -5865,27 +5865,27 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>WSSS70YB</t>
+          <t>12IP6720</t>
         </is>
       </c>
       <c r="B181" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C181" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D181" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
@@ -5901,20 +5901,20 @@
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>CL2RBM5PK</t>
+          <t>CBSF100</t>
         </is>
       </c>
       <c r="B182" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C182" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D182" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E182" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
@@ -5930,20 +5930,20 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>24IP20200</t>
+          <t>CBSF75</t>
         </is>
       </c>
       <c r="B183" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C183" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D183" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E183" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
@@ -5952,27 +5952,27 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>LHNSE27RO</t>
+          <t>CL2RBM5PK</t>
         </is>
       </c>
       <c r="B184" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C184" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D184" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E184" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
@@ -5988,20 +5988,20 @@
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320YE-DE</t>
+          <t>COS93BM3PK</t>
         </is>
       </c>
       <c r="B185" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C185" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D185" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
@@ -6010,14 +6010,14 @@
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+WCLDBM+ICT185E2760</t>
+          <t>CRSF100BM+PHHT1PBRBM+LSHM400HE</t>
         </is>
       </c>
       <c r="B186" s="8" t="n">
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="D186" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E186" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
@@ -6046,20 +6046,20 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>O2-PV99-0CIB</t>
+          <t>ENC7499</t>
         </is>
       </c>
       <c r="B187" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C187" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D187" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
@@ -6068,24 +6068,24 @@
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>CBSF75</t>
+          <t>LDMG80E2743PK</t>
         </is>
       </c>
       <c r="B188" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C188" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D188" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E188" s="8" t="n">
         <v>14</v>
@@ -6097,24 +6097,24 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>LDWWE279</t>
+          <t>LDMST64E2783PK</t>
         </is>
       </c>
       <c r="B189" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C189" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D189" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E189" s="8" t="n">
         <v>14</v>
@@ -6126,24 +6126,24 @@
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>12IP20500</t>
+          <t>LDWWE279</t>
         </is>
       </c>
       <c r="B190" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C190" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D190" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E190" s="8" t="n">
         <v>14</v>
@@ -6155,21 +6155,21 @@
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSLS155BM</t>
+          <t>O2-PV99-0CIB</t>
         </is>
       </c>
       <c r="B191" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C191" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D191" s="8" t="n">
         <v>0</v>
@@ -6184,24 +6184,24 @@
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BD+RPR44WH</t>
+          <t>PHCD1PBRBW+LSTM310BM</t>
         </is>
       </c>
       <c r="B192" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" s="8" t="n">
         <v>14</v>
-      </c>
-      <c r="D192" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E192" s="8" t="n">
         <v>14</v>
@@ -6213,27 +6213,27 @@
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>WJBIP685BM</t>
+          <t>12IP20500</t>
         </is>
       </c>
       <c r="B193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="E193" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
@@ -6242,27 +6242,27 @@
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM</t>
+          <t>24IP67100</t>
         </is>
       </c>
       <c r="B194" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C194" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D194" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E194" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
@@ -6278,20 +6278,20 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>24IP67100</t>
+          <t>24IP67200</t>
         </is>
       </c>
       <c r="B195" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C195" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D195" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E195" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
@@ -6300,27 +6300,27 @@
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>24IP67200</t>
+          <t>24IP6724</t>
         </is>
       </c>
       <c r="B196" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C196" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D196" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E196" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
@@ -6329,27 +6329,27 @@
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BU-JJ</t>
+          <t>CCBC5</t>
         </is>
       </c>
       <c r="B197" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C197" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D197" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E197" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
@@ -6358,27 +6358,27 @@
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>24IP6760</t>
+          <t>CL2TIV</t>
         </is>
       </c>
       <c r="B198" s="8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C198" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D198" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E198" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
@@ -6387,27 +6387,27 @@
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>LDMG80E2742PK</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM-JJ</t>
         </is>
       </c>
       <c r="B199" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C199" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D199" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E199" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
@@ -6416,27 +6416,27 @@
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>12BO18</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290GR-JJ</t>
         </is>
       </c>
       <c r="B200" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C200" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D200" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E200" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
@@ -6445,14 +6445,14 @@
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>WCB7WH+RPR44WH</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290YE-JJ</t>
         </is>
       </c>
       <c r="B201" s="8" t="n">
@@ -6462,10 +6462,10 @@
         <v>13</v>
       </c>
       <c r="D201" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>LHNSE27CO</t>
+          <t>CRSF100BM+WSCH135BM+LSHH240BM+ICST64E27</t>
         </is>
       </c>
       <c r="B202" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C202" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D202" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E202" s="8" t="n">
         <v>13</v>
@@ -6503,24 +6503,24 @@
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>CCBC5</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320BT-DE</t>
         </is>
       </c>
       <c r="B203" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C203" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D203" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E203" s="8" t="n">
         <v>13</v>
@@ -6532,24 +6532,24 @@
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>CCBC3</t>
+          <t>CRSF120YB+WSRH230YB+LSMS320GR</t>
         </is>
       </c>
       <c r="B204" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C204" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D204" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E204" s="8" t="n">
         <v>13</v>
@@ -6561,24 +6561,24 @@
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>PHSHF1PBRYB+LSSS300BM+ICST64E2740</t>
+          <t>LDMG80E2742PK</t>
         </is>
       </c>
       <c r="B205" s="8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C205" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D205" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E205" s="8" t="n">
         <v>13</v>
@@ -6590,24 +6590,24 @@
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>CRSF108CO+WSST70CO+ICST64E2740</t>
+          <t>PCBS16T10BM3PK</t>
         </is>
       </c>
       <c r="B206" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C206" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D206" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E206" s="8" t="n">
         <v>13</v>
@@ -6619,24 +6619,24 @@
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>LHC4E27WH</t>
+          <t>PHSH1PBRYB</t>
         </is>
       </c>
       <c r="B207" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C207" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="C207" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D207" s="8" t="n">
-        <v>10</v>
       </c>
       <c r="E207" s="8" t="n">
         <v>13</v>
@@ -6655,17 +6655,17 @@
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>PHSH1PBRCO</t>
+          <t>PHSHF1PBRYB+LSSS300BM+ICST64E2740</t>
         </is>
       </c>
       <c r="B208" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C208" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D208" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E208" s="8" t="n">
         <v>13</v>
@@ -6677,24 +6677,24 @@
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>CL2THEAPK</t>
+          <t>WCB7BM+RPR44WH_DE</t>
         </is>
       </c>
       <c r="B209" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C209" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D209" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E209" s="8" t="n">
         <v>13</v>
@@ -6706,14 +6706,14 @@
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>CL2TIV</t>
+          <t>WSLH200BM</t>
         </is>
       </c>
       <c r="B210" s="8" t="n">
@@ -6742,17 +6742,17 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSCH135BM+LSHH240BM+ICST64E27</t>
+          <t>WSNWBM+LSCY290BM</t>
         </is>
       </c>
       <c r="B211" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C211" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D211" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E211" s="8" t="n">
         <v>13</v>
@@ -6764,27 +6764,27 @@
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>WCB7BM+RPR44WH_DE</t>
+          <t>12BO282PK</t>
         </is>
       </c>
       <c r="B212" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C212" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D212" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E212" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
@@ -6793,27 +6793,27 @@
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>24IP6724</t>
+          <t>12IP20200</t>
         </is>
       </c>
       <c r="B213" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C213" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D213" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E213" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
@@ -6822,27 +6822,27 @@
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290OR-JJ</t>
+          <t>BC3W50</t>
         </is>
       </c>
       <c r="B214" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C214" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D214" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E214" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
@@ -6851,27 +6851,27 @@
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>PHCD1PBRBW+LSTM310BM</t>
+          <t>CCBKNWE50</t>
         </is>
       </c>
       <c r="B215" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C215" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D215" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E215" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
@@ -6880,27 +6880,27 @@
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320BT-DE</t>
+          <t>CL3RGD</t>
         </is>
       </c>
       <c r="B216" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C216" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D216" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E216" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
@@ -6909,27 +6909,27 @@
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E278APK</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GR</t>
         </is>
       </c>
       <c r="B217" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D217" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E217" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
@@ -6938,27 +6938,27 @@
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>CL2RBM</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY-JJ</t>
         </is>
       </c>
       <c r="B218" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C218" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D218" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E218" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
@@ -6967,27 +6967,27 @@
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>WLRPE27BM</t>
+          <t>CRSF100BM+WSAFT200BG</t>
         </is>
       </c>
       <c r="B219" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C219" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D219" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E219" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
@@ -6996,24 +6996,24 @@
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>WSLH200BM+ICST64E27</t>
+          <t>CRSF100OR</t>
         </is>
       </c>
       <c r="B220" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C220" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D220" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E220" s="8" t="n">
         <v>12</v>
@@ -7025,14 +7025,14 @@
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>LSDO300SN+RPR44WH</t>
+          <t>CRSF100WH+PHTT1PCRCH</t>
         </is>
       </c>
       <c r="B221" s="8" t="n">
@@ -7061,17 +7061,17 @@
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+WSSS70YB+LSFT220BC</t>
+          <t>CRSF108CO+WSST70CO+ICST64E2740</t>
         </is>
       </c>
       <c r="B222" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C222" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D222" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E222" s="8" t="n">
         <v>12</v>
@@ -7083,24 +7083,24 @@
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>5IP2028</t>
+          <t>LDMST64E278APK</t>
         </is>
       </c>
       <c r="B223" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C223" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D223" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E223" s="8" t="n">
         <v>12</v>
@@ -7112,21 +7112,21 @@
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>WCCYSP160GD</t>
+          <t>LSCY290BC+RPR44WH G</t>
         </is>
       </c>
       <c r="B224" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="C224" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>0</v>
@@ -7141,24 +7141,24 @@
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>BC3W50</t>
+          <t>LSCY290BD+RPR44WH</t>
         </is>
       </c>
       <c r="B225" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C225" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D225" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E225" s="8" t="n">
         <v>12</v>
@@ -7170,24 +7170,24 @@
       </c>
       <c r="G225" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>CCBC24</t>
+          <t>LSDO300SN+RPR44WH</t>
         </is>
       </c>
       <c r="B226" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C226" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D226" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E226" s="8" t="n">
         <v>12</v>
@@ -7199,24 +7199,24 @@
       </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>12BO282PK</t>
+          <t>PHCD1PBRBW+LSCY290BC</t>
         </is>
       </c>
       <c r="B227" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C227" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D227" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E227" s="8" t="n">
         <v>12</v>
@@ -7228,24 +7228,24 @@
       </c>
       <c r="G227" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSHM300HE</t>
+          <t>PHSHF1PBRYB+LSSS300BS+ICST64E27</t>
         </is>
       </c>
       <c r="B228" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C228" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D228" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E228" s="8" t="n">
         <v>12</v>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G228" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>LDMT45E2742PK</t>
+          <t>SPSDP2WH3PK</t>
         </is>
       </c>
       <c r="B230" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C230" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D230" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E230" s="8" t="n">
         <v>12</v>
@@ -7315,21 +7315,21 @@
       </c>
       <c r="G230" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290GR-JJ</t>
+          <t>WCCYSP160GD</t>
         </is>
       </c>
       <c r="B231" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C231" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D231" s="8" t="n">
         <v>0</v>
@@ -7344,24 +7344,24 @@
       </c>
       <c r="G231" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>CRSF100WH+PHTT1PCRCH</t>
+          <t>WLRPE27BM</t>
         </is>
       </c>
       <c r="B232" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="C232" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D232" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E232" s="8" t="n">
         <v>12</v>
@@ -7373,14 +7373,14 @@
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>PHSHF1PBRYB+LSSS300BS+ICST64E27</t>
+          <t>WSLH200BM+ICST64E27</t>
         </is>
       </c>
       <c r="B233" s="8" t="n">
@@ -7409,11 +7409,11 @@
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>CL2TGD</t>
+          <t>5IP2028</t>
         </is>
       </c>
       <c r="B234" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C234" s="8" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
         <v>11</v>
       </c>
       <c r="E234" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
@@ -7431,18 +7431,18 @@
       </c>
       <c r="G234" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>CL3RGD</t>
+          <t>5IP2030</t>
         </is>
       </c>
       <c r="B235" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C235" s="8" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
         <v>10</v>
       </c>
       <c r="E235" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
@@ -7467,20 +7467,20 @@
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BC+RPR44WH G</t>
+          <t>CC5/W</t>
         </is>
       </c>
       <c r="B236" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C236" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D236" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E236" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F236" s="7" t="inlineStr">
         <is>
@@ -7496,20 +7496,20 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>12IP20200</t>
+          <t>CCBC24</t>
         </is>
       </c>
       <c r="B237" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C237" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D237" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E237" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F237" s="7" t="inlineStr">
         <is>
@@ -7518,24 +7518,24 @@
       </c>
       <c r="G237" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE7-IFR</t>
+          <t>CCBC3</t>
         </is>
       </c>
       <c r="B238" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C238" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="D238" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E238" s="8" t="n">
         <v>11</v>
@@ -7547,21 +7547,21 @@
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCN1PBRBM</t>
+          <t>CCBKNWE7-IFR</t>
         </is>
       </c>
       <c r="B239" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="C239" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D239" s="8" t="n">
         <v>0</v>
@@ -7576,24 +7576,24 @@
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>IMWWFPK</t>
+          <t>CL3THE</t>
         </is>
       </c>
       <c r="B240" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="C240" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D240" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E240" s="8" t="n">
         <v>11</v>
@@ -7605,24 +7605,24 @@
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>CC5/W</t>
+          <t>COS92BM5PK</t>
         </is>
       </c>
       <c r="B241" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C241" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="D241" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E241" s="8" t="n">
         <v>11</v>
@@ -7634,24 +7634,24 @@
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM-JJ</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70BM+LSWD360BC</t>
         </is>
       </c>
       <c r="B242" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C242" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="D242" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E242" s="8" t="n">
         <v>11</v>
@@ -7663,24 +7663,24 @@
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>LDST185E2742PK</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BI_DE</t>
         </is>
       </c>
       <c r="B243" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C243" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D243" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E243" s="8" t="n">
         <v>11</v>
@@ -7692,21 +7692,21 @@
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+ICST64E27_DE</t>
+          <t>CRSF100BM+PHCN1PBRBM</t>
         </is>
       </c>
       <c r="B244" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C244" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D244" s="8" t="n">
         <v>0</v>
@@ -7721,21 +7721,21 @@
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>LSDO300BI+RPR44WH</t>
+          <t>CRSF100BM+PHHT1PBRBM+ICST64E27_DE</t>
         </is>
       </c>
       <c r="B245" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="C245" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D245" s="8" t="n">
         <v>0</v>
@@ -7750,24 +7750,24 @@
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>COS92BM5PK</t>
+          <t>CRSF100GY+PHCH1PWRSGY+LSSS300GY</t>
         </is>
       </c>
       <c r="B246" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C246" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D246" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E246" s="8" t="n">
         <v>11</v>
@@ -7779,21 +7779,21 @@
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E2786PK</t>
+          <t>IMCWFPK L</t>
         </is>
       </c>
       <c r="B247" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="C247" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D247" s="8" t="n">
         <v>0</v>
@@ -7808,21 +7808,21 @@
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BI_DE</t>
+          <t>LDMG95E2786PK</t>
         </is>
       </c>
       <c r="B248" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C248" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D248" s="8" t="n">
         <v>0</v>
@@ -7837,24 +7837,24 @@
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70BM+LSWD360BC</t>
+          <t>LSCY290YB+RPR44WH</t>
         </is>
       </c>
       <c r="B249" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C249" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D249" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E249" s="8" t="n">
         <v>11</v>
@@ -7866,21 +7866,21 @@
       </c>
       <c r="G249" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GR</t>
+          <t>LSDO300BI+RPR44WH</t>
         </is>
       </c>
       <c r="B250" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C250" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D250" s="8" t="n">
         <v>0</v>
@@ -7895,24 +7895,24 @@
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>WSNWBM+LSCY290BM</t>
+          <t>PHHR1HETHE</t>
         </is>
       </c>
       <c r="B251" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C251" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D251" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E251" s="8" t="n">
         <v>11</v>
@@ -7924,24 +7924,24 @@
       </c>
       <c r="G251" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>CL3RGY</t>
+          <t>TPOSBDBM</t>
         </is>
       </c>
       <c r="B252" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C252" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D252" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E252" s="8" t="n">
         <v>11</v>
@@ -7953,27 +7953,27 @@
       </c>
       <c r="G252" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>LSCY290YB+RPR44WH</t>
+          <t>12DE2P2A</t>
         </is>
       </c>
       <c r="B253" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C253" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D253" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E253" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
@@ -7982,27 +7982,27 @@
       </c>
       <c r="G253" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>CRSF100GY+PHCH1PWRSGY+LSSS300GY</t>
+          <t>24IP6720</t>
         </is>
       </c>
       <c r="B254" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C254" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D254" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E254" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F254" s="7" t="inlineStr">
         <is>
@@ -8011,27 +8011,27 @@
       </c>
       <c r="G254" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>IMCWFPK L</t>
+          <t>CCBC7.2</t>
         </is>
       </c>
       <c r="B255" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C255" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D255" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E255" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
@@ -8047,20 +8047,20 @@
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>PLMJBC+LDMST64E2742PK</t>
+          <t>CL3TBR</t>
         </is>
       </c>
       <c r="B256" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C256" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D256" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E256" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
@@ -8069,24 +8069,24 @@
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY-JJ</t>
+          <t>CL3TOR</t>
         </is>
       </c>
       <c r="B257" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C257" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D257" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E257" s="8" t="n">
         <v>10</v>
@@ -8098,14 +8098,14 @@
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+LHNSE27YB+SCRN70YB+LSCY290BS</t>
+          <t>CL3TRO</t>
         </is>
       </c>
       <c r="B258" s="8" t="n">
@@ -8134,17 +8134,17 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>PHUH1HETBM+LSHM300HE_M2</t>
+          <t>CRFF108CO+WSSS70CO+SCRN70CO</t>
         </is>
       </c>
       <c r="B259" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C259" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D259" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E259" s="8" t="n">
         <v>10</v>
@@ -8156,21 +8156,21 @@
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>LSBLP3BCR</t>
+          <t>CRSF100BM+WSCH135BM+SCRN70BM+LSTF40GB</t>
         </is>
       </c>
       <c r="B260" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C260" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D260" s="8" t="n">
         <v>0</v>
@@ -8185,24 +8185,24 @@
       </c>
       <c r="G260" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>24IP6715</t>
+          <t>CRSF100BM+WSHR135BM+LSFT220GY</t>
         </is>
       </c>
       <c r="B261" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C261" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D261" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E261" s="8" t="n">
         <v>10</v>
@@ -8214,14 +8214,14 @@
       </c>
       <c r="G261" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>12DE2P2A</t>
+          <t>CRSF100BM2PK</t>
         </is>
       </c>
       <c r="B262" s="8" t="n">
@@ -8250,17 +8250,17 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>LSLT360BC2PK+RPR44WH2PK_DE</t>
+          <t>CRSF100CO+CL3TBR+LHSHE27YB</t>
         </is>
       </c>
       <c r="B263" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C263" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D263" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E263" s="8" t="n">
         <v>10</v>
@@ -8272,24 +8272,24 @@
       </c>
       <c r="G263" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>CRFF108CO+WSSS70CO+SCRN70CO</t>
+          <t>CRSF100GB+PHHA1PBRYB+LSRP260GB</t>
         </is>
       </c>
       <c r="B264" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C264" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D264" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E264" s="8" t="n">
         <v>10</v>
@@ -8301,14 +8301,14 @@
       </c>
       <c r="G264" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CRSF1203WH+PHTT1PWR1WH3PK+SPSPLBM3PK</t>
+          <t>CRSF100RE+PHCH1PWRSRE+LSFT220RE</t>
         </is>
       </c>
       <c r="B265" s="8" t="n">
@@ -8337,7 +8337,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E2784PK</t>
+          <t>CRSF100YB+LHNSE27YB+SCRN70YB+LSCY290BS</t>
         </is>
       </c>
       <c r="B266" s="8" t="n">
@@ -8366,14 +8366,14 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>LDLIE27SR4</t>
+          <t>CRSF1203WH+PHTT1PWR1WH3PK+SPSPLBM3PK</t>
         </is>
       </c>
       <c r="B267" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C267" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D267" s="8" t="n">
         <v>0</v>
@@ -8388,14 +8388,14 @@
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>CRSF100GB+PHHA1PBRYB+LSRP260GB</t>
+          <t>LDED105E273</t>
         </is>
       </c>
       <c r="B268" s="8" t="n">
@@ -8424,14 +8424,14 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CCBC7.2</t>
+          <t>LDLIE27SR4</t>
         </is>
       </c>
       <c r="B269" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C269" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D269" s="8" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="G269" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CO+CL3TBR+LHSHE27YB</t>
+          <t>LDMT45E2742PK</t>
         </is>
       </c>
       <c r="B270" s="8" t="n">
@@ -8482,17 +8482,17 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>SFCR3PBK</t>
+          <t>LDST185E2742PK</t>
         </is>
       </c>
       <c r="B271" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C271" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D271" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E271" s="8" t="n">
         <v>10</v>
@@ -8504,24 +8504,24 @@
       </c>
       <c r="G271" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>CL3TBR</t>
+          <t>LSBLP3BCR</t>
         </is>
       </c>
       <c r="B272" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C272" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D272" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E272" s="8" t="n">
         <v>10</v>
@@ -8533,21 +8533,21 @@
       </c>
       <c r="G272" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CL3TRO</t>
+          <t>LSCY290BC+RPR44WH M2</t>
         </is>
       </c>
       <c r="B273" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C273" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D273" s="8" t="n">
         <v>0</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G273" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
@@ -8598,17 +8598,17 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CCBC12</t>
+          <t>LSLT360BC2PK+RPR44WH2PK_DE</t>
         </is>
       </c>
       <c r="B275" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C275" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D275" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E275" s="8" t="n">
         <v>10</v>
@@ -8620,24 +8620,24 @@
       </c>
       <c r="G275" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>CL3TOR</t>
+          <t>PHCD1PBRBW+LSCY210BM</t>
         </is>
       </c>
       <c r="B276" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C276" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D276" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E276" s="8" t="n">
         <v>10</v>
@@ -8649,14 +8649,14 @@
       </c>
       <c r="G276" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290YE-JJ</t>
+          <t>PHUH1HETBM+LSHM300HE_M2</t>
         </is>
       </c>
       <c r="B277" s="8" t="n">
@@ -8685,14 +8685,14 @@
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>LDED105E273</t>
+          <t>SFCR3PBK</t>
         </is>
       </c>
       <c r="B278" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C278" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C278" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D278" s="8" t="n">
         <v>0</v>
@@ -8707,24 +8707,24 @@
       </c>
       <c r="G278" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSCH135BM+SCRN70BM+LSTF40GB</t>
+          <t>WJBIP686BM2PK</t>
         </is>
       </c>
       <c r="B279" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C279" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D279" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E279" s="8" t="n">
         <v>10</v>
@@ -8736,24 +8736,24 @@
       </c>
       <c r="G279" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="7" t="inlineStr">
         <is>
-          <t>LSCY290WH+RPR44WH W</t>
+          <t>WLGI350E27BM</t>
         </is>
       </c>
       <c r="B280" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C280" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D280" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E280" s="8" t="n">
         <v>10</v>
@@ -8765,56 +8765,56 @@
       </c>
       <c r="G280" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="7" t="inlineStr">
-        <is>
-          <t>CRSF100RE+PHCH1PWRSRE+LSFT220RE</t>
-        </is>
-      </c>
-      <c r="B281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C281" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E281" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F281" s="7" t="inlineStr">
-        <is>
-          <t>Missing channel</t>
-        </is>
-      </c>
-      <c r="G281" s="7" t="inlineStr">
-        <is>
-          <t>Create Shopify + eBay listing</t>
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>LHSHE27CO</t>
+        </is>
+      </c>
+      <c r="B281" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="C281" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D281" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E281" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="F281" s="9" t="inlineStr">
+        <is>
+          <t>Shopify winner</t>
+        </is>
+      </c>
+      <c r="G281" s="9" t="inlineStr">
+        <is>
+          <t>Improve Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>LHSHE27CO</t>
+          <t>12BO72</t>
         </is>
       </c>
       <c r="B282" s="10" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C282" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D282" s="10" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E282" s="10" t="n">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
@@ -8830,20 +8830,20 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>12BO72</t>
+          <t>LSCY210BG+RPR44WH</t>
         </is>
       </c>
       <c r="B283" s="10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C283" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D283" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D283" s="10" t="n">
-        <v>21</v>
-      </c>
       <c r="E283" s="10" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="G283" s="9" t="inlineStr">
         <is>
-          <t>Improve Amazon listing</t>
+          <t>Improve Amazon/eBay listing</t>
         </is>
       </c>
     </row>
@@ -8863,16 +8863,16 @@
         </is>
       </c>
       <c r="B284" s="10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C284" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D284" s="10" t="n">
         <v>3</v>
       </c>
       <c r="E284" s="10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-021_channel-opportunity/evidence/final_outputs/REQ-24_channel-opportunity/REQ-24-D01_channel_opportunity.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-021_channel-opportunity/evidence/final_outputs/REQ-24_channel-opportunity/REQ-24-D01_channel_opportunity.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Opportunity" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Channel Opportunity'!$A$1:$G$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Channel Opportunity'!$A$1:$G$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -531,7 +531,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Window: rolling 90 days, data through 2026-08-10 (last complete day).</t>
+          <t>Window: rolling 90 days, data through 2026-08-11 (last complete day).</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G284"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -717,13 +717,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1145,20 +1145,20 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E274</t>
+          <t>LHSHE27BA</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1174,20 +1174,20 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>LHSHE27BA</t>
+          <t>LDMG95E274</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
         <v>0</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -1348,20 +1348,20 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM-JJ</t>
+          <t>CCBKNWE7</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -1370,24 +1370,24 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE7</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BM-JJ</t>
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
         <v>57</v>
@@ -1399,24 +1399,24 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM</t>
+          <t>LSMS320RE+RPR44WH</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8" t="n">
         <v>56</v>
@@ -1428,27 +1428,27 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>LSMS320RE+RPR44WH</t>
+          <t>CRSF100BM</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -1561,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>12IP2060</t>
+          <t>12IP20100</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="E37" s="8" t="n">
-        <v>46</v>
-      </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Missing channel</t>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -1783,20 +1783,20 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>12IP20100</t>
+          <t>12IP2060</t>
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
@@ -1899,17 +1899,17 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BG+RPR44WH</t>
+          <t>CCBKNWE12</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E44" s="8" t="n">
         <v>41</v>
@@ -1928,20 +1928,20 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE12</t>
+          <t>LSCY290BG+RPR44WH</t>
         </is>
       </c>
       <c r="B45" s="8" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -1957,20 +1957,20 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>12IP20150</t>
+          <t>COS92BM</t>
         </is>
       </c>
       <c r="B46" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -1979,27 +1979,27 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>COS92BM</t>
+          <t>12IP20150</t>
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -2008,24 +2008,24 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>5IP2050</t>
+          <t>CCBKNWE18</t>
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E48" s="8" t="n">
         <v>38</v>
@@ -2044,20 +2044,20 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE18</t>
+          <t>24IP6710</t>
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -2073,17 +2073,17 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>CL3TGL</t>
+          <t>5IP2050</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E50" s="8" t="n">
         <v>37</v>
@@ -2102,20 +2102,20 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>24IP6710</t>
+          <t>CL3TGL</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -2305,20 +2305,20 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>12BO28</t>
+          <t>PHUH2HETBM</t>
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C58" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -2327,24 +2327,24 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>12IP2080</t>
+          <t>12BO28</t>
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E59" s="8" t="n">
         <v>32</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -2450,17 +2450,17 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>PHUH2HETBM</t>
+          <t>12IP2080</t>
         </is>
       </c>
       <c r="B63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="8" t="n">
         <v>31</v>
-      </c>
-      <c r="C63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E63" s="8" t="n">
         <v>31</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>12IP2030</t>
+          <t>LDMT45E274</t>
         </is>
       </c>
       <c r="B64" s="8" t="n">
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
@@ -2508,17 +2508,17 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>5IP2010</t>
+          <t>12IP2030</t>
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E65" s="8" t="n">
         <v>30</v>
@@ -2530,24 +2530,24 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>LDMT45E274</t>
+          <t>12IP67150</t>
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C66" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E66" s="8" t="n">
         <v>30</v>
@@ -2566,20 +2566,20 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>12IP67150</t>
+          <t>5IP2010</t>
         </is>
       </c>
       <c r="B67" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C67" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
@@ -2740,20 +2740,20 @@
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>PHCH1BMRBM+LSCY290BG-TJ</t>
+          <t>12IP20400</t>
         </is>
       </c>
       <c r="B73" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C73" s="8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
@@ -2762,24 +2762,24 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>12IP20400</t>
+          <t>CCBKNWE25</t>
         </is>
       </c>
       <c r="B74" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E74" s="8" t="n">
         <v>27</v>
@@ -2856,14 +2856,14 @@
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>PHHT2PBRBM</t>
+          <t>PHCH1BMRBM+LSCY290BG-TJ</t>
         </is>
       </c>
       <c r="B77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="8" t="n">
         <v>27</v>
-      </c>
-      <c r="C77" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D77" s="8" t="n">
         <v>0</v>
@@ -2878,24 +2878,24 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>WJBIP685BM2PK</t>
+          <t>PHHT2PBRBM</t>
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E78" s="8" t="n">
         <v>27</v>
@@ -2907,14 +2907,14 @@
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>CCGNNWE48</t>
+          <t>WJBIP685BM2PK</t>
         </is>
       </c>
       <c r="B79" s="8" t="n">
@@ -2924,10 +2924,10 @@
         <v>0</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -2943,17 +2943,17 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>CRFF500BM+PHCH1BMRBM3PK+LSCY210BG3PK-J</t>
+          <t>LHTHE27CO</t>
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E80" s="8" t="n">
         <v>26</v>
@@ -2965,24 +2965,24 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27CO</t>
+          <t>PHHCF1BMRYB</t>
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C81" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E81" s="8" t="n">
         <v>26</v>
@@ -2994,27 +2994,27 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>PHHCF1BMRYB</t>
+          <t>CCGNNWE48</t>
         </is>
       </c>
       <c r="B82" s="8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C82" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
@@ -3023,24 +3023,24 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE25</t>
+          <t>CRFF500BM+PHCH1BMRBM3PK+LSCY210BG3PK-J</t>
         </is>
       </c>
       <c r="B83" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C83" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E83" s="8" t="n">
         <v>25</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
@@ -3262,17 +3262,17 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>12IP20600</t>
+          <t>24IP20400</t>
         </is>
       </c>
       <c r="B91" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C91" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E91" s="8" t="n">
         <v>23</v>
@@ -3291,17 +3291,17 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>24IP20400</t>
+          <t>24IP20480</t>
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C92" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E92" s="8" t="n">
         <v>23</v>
@@ -3320,17 +3320,17 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>24IP20480</t>
+          <t>24IP67120</t>
         </is>
       </c>
       <c r="B93" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C93" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E93" s="8" t="n">
         <v>23</v>
@@ -3342,24 +3342,24 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>24IP67120</t>
+          <t>CNP1000YB</t>
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C94" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E94" s="8" t="n">
         <v>23</v>
@@ -3371,24 +3371,24 @@
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>CNP1000YB</t>
+          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C95" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E95" s="8" t="n">
         <v>23</v>
@@ -3400,24 +3400,24 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRYB+SCRN70BM+LSOL180BG</t>
+          <t>KNNT1- 74 B</t>
         </is>
       </c>
       <c r="B96" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E96" s="8" t="n">
         <v>23</v>
@@ -3429,14 +3429,14 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>KNNT1- 74 B</t>
+          <t>LSCY290WH+RPR44WH C</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -3465,7 +3465,7 @@
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>LSCY290WH+RPR44WH C</t>
+          <t>LSDO300BI2PK+RPR44WH2PK_DE</t>
         </is>
       </c>
       <c r="B98" s="8" t="n">
@@ -3494,17 +3494,17 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>LSDO300BI2PK+RPR44WH2PK_DE</t>
+          <t>WJBIP68T13BM2PK</t>
         </is>
       </c>
       <c r="B99" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="8" t="n">
         <v>23</v>
-      </c>
-      <c r="D99" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E99" s="8" t="n">
         <v>23</v>
@@ -3516,27 +3516,27 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>WJBIP68T13BM2PK</t>
+          <t>12IP20600</t>
         </is>
       </c>
       <c r="B100" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C100" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E100" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -3610,17 +3610,17 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>LHC2E27WH</t>
+          <t>LSCP150WH2PK+RPR44WH2PK</t>
         </is>
       </c>
       <c r="B103" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E103" s="8" t="n">
         <v>22</v>
@@ -3632,24 +3632,24 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>LSCP150WH2PK+RPR44WH2PK</t>
+          <t>PHUH1HETBM</t>
         </is>
       </c>
       <c r="B104" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C104" s="8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" s="8" t="n">
         <v>22</v>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -3697,17 +3697,17 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>24IP20360</t>
+          <t>5IP2020</t>
         </is>
       </c>
       <c r="B106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E106" s="8" t="n">
         <v>21</v>
@@ -3719,24 +3719,24 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>5IP2020</t>
+          <t>CCGNNWE24</t>
         </is>
       </c>
       <c r="B107" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C107" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E107" s="8" t="n">
         <v>21</v>
@@ -3755,17 +3755,17 @@
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>CCGNNWE24</t>
+          <t>CL2TGY</t>
         </is>
       </c>
       <c r="B108" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C108" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E108" s="8" t="n">
         <v>21</v>
@@ -3777,24 +3777,24 @@
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>CL2TGY</t>
+          <t>CRSF100BM+WSLS155BM</t>
         </is>
       </c>
       <c r="B109" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C109" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E109" s="8" t="n">
         <v>21</v>
@@ -3806,24 +3806,24 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSLS155BM</t>
+          <t>LHC2E27WH</t>
         </is>
       </c>
       <c r="B110" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C110" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E110" s="8" t="n">
         <v>21</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
@@ -3871,17 +3871,17 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>PHUH1HETBM</t>
+          <t>WSNWBM+LSCY290BM+LDMST64E274</t>
         </is>
       </c>
       <c r="B112" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C112" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="8" t="n">
         <v>21</v>
@@ -3893,27 +3893,27 @@
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>WJBIP686BM</t>
+          <t>12SIP67100</t>
         </is>
       </c>
       <c r="B113" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C113" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E113" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
@@ -3929,20 +3929,20 @@
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>WSNWBM+LSCY290BM+LDMST64E274</t>
+          <t>24IP20360</t>
         </is>
       </c>
       <c r="B114" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C114" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E114" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
@@ -3951,24 +3951,24 @@
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>12SIP67100</t>
+          <t>COI9BBM2PK</t>
         </is>
       </c>
       <c r="B115" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E115" s="8" t="n">
         <v>20</v>
@@ -3980,24 +3980,24 @@
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>COI9BBM2PK</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320RE</t>
         </is>
       </c>
       <c r="B116" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E116" s="8" t="n">
         <v>20</v>
@@ -4009,14 +4009,14 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320RE</t>
+          <t>CRSF100BM+PHDO1PBRBM+LSTM310BM</t>
         </is>
       </c>
       <c r="B117" s="8" t="n">
@@ -4045,17 +4045,17 @@
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHDO1PBRBM+LSTM310BM</t>
+          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
         </is>
       </c>
       <c r="B118" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C118" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E118" s="8" t="n">
         <v>20</v>
@@ -4067,24 +4067,24 @@
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSMS320BI</t>
+          <t>CRSF100BM+PHRI1PBRBY+LSDO210BG_DE</t>
         </is>
       </c>
       <c r="B119" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C119" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E119" s="8" t="n">
         <v>20</v>
@@ -4096,14 +4096,14 @@
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHRI1PBRBY+LSDO210BG_DE</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290WH-JJ</t>
         </is>
       </c>
       <c r="B120" s="8" t="n">
@@ -4132,14 +4132,14 @@
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290WH-JJ</t>
+          <t>CRSF100YE+WSCH135YE+LSDO210YE</t>
         </is>
       </c>
       <c r="B121" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C121" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D121" s="8" t="n">
         <v>0</v>
@@ -4154,24 +4154,24 @@
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YE+WSCH135YE+LSDO210YE</t>
+          <t>LDMG95E2782PK</t>
         </is>
       </c>
       <c r="B122" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C122" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D122" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E122" s="8" t="n">
         <v>20</v>
@@ -4183,24 +4183,24 @@
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E2782PK</t>
+          <t>LHTHE27GB</t>
         </is>
       </c>
       <c r="B123" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C123" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E123" s="8" t="n">
         <v>20</v>
@@ -4219,17 +4219,17 @@
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27GB</t>
+          <t>LSCY210BG3PK</t>
         </is>
       </c>
       <c r="B124" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C124" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E124" s="8" t="n">
         <v>20</v>
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>LSCY210BG3PK</t>
+          <t>WJBIP686BM</t>
         </is>
       </c>
       <c r="B125" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C125" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E125" s="8" t="n">
         <v>20</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
@@ -4335,17 +4335,17 @@
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>CCBC7</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320BI</t>
         </is>
       </c>
       <c r="B128" s="8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C128" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E128" s="8" t="n">
         <v>19</v>
@@ -4357,21 +4357,21 @@
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70YB+LSMS320BI</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C129" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D129" s="8" t="n">
         <v>0</v>
@@ -4386,21 +4386,21 @@
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY</t>
+          <t>ENC3611</t>
         </is>
       </c>
       <c r="B130" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C130" s="8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D130" s="8" t="n">
         <v>0</v>
@@ -4415,24 +4415,24 @@
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E2742PK</t>
+          <t>LDMST64E276</t>
         </is>
       </c>
       <c r="B131" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E131" s="8" t="n">
         <v>19</v>
@@ -4451,20 +4451,20 @@
     <row r="132">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E276</t>
+          <t>12IP67120OL2</t>
         </is>
       </c>
       <c r="B132" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C132" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
@@ -4480,17 +4480,17 @@
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>12IP67120OL2</t>
+          <t>12IP67350</t>
         </is>
       </c>
       <c r="B133" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C133" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" s="8" t="n">
         <v>18</v>
@@ -4567,17 +4567,17 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>5IP20150</t>
+          <t>24IP6736</t>
         </is>
       </c>
       <c r="B136" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C136" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E136" s="8" t="n">
         <v>18</v>
@@ -4596,17 +4596,17 @@
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>CL3TBU</t>
+          <t>5IP20150</t>
         </is>
       </c>
       <c r="B137" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E137" s="8" t="n">
         <v>18</v>
@@ -4625,17 +4625,17 @@
     <row r="138">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+WSSS70YB+LSFT220BC</t>
+          <t>CL3TBU</t>
         </is>
       </c>
       <c r="B138" s="8" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C138" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E138" s="8" t="n">
         <v>18</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>ENC3611</t>
+          <t>CRSF100YB+WSSS70YB+LSFT220BC</t>
         </is>
       </c>
       <c r="B139" s="8" t="n">
@@ -4712,17 +4712,17 @@
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>LSFT220WH+RPR44WH</t>
+          <t>LDMST64E2742PK</t>
         </is>
       </c>
       <c r="B141" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C141" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E141" s="8" t="n">
         <v>18</v>
@@ -4741,17 +4741,17 @@
     <row r="142">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>LSMS320BI+RPR44WH D</t>
+          <t>LSFT220WH+RPR44WH</t>
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C142" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E142" s="8" t="n">
         <v>18</v>
@@ -4763,14 +4763,14 @@
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>PHCT1BMRBM+PHBA1BMRBM+LSDO300BM</t>
+          <t>LSMS320BI+RPR44WH D</t>
         </is>
       </c>
       <c r="B143" s="8" t="n">
@@ -4799,14 +4799,14 @@
     <row r="144">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>PLOTBM+LSFT220BM</t>
+          <t>PHCT1BMRBM+PHBA1BMRBM+LSDO300BM</t>
         </is>
       </c>
       <c r="B144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" s="8" t="n">
         <v>18</v>
-      </c>
-      <c r="C144" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D144" s="8" t="n">
         <v>0</v>
@@ -4821,14 +4821,14 @@
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>WLHSBMSQ10</t>
+          <t>PLOTBM+LSFT220BM</t>
         </is>
       </c>
       <c r="B145" s="8" t="n">
@@ -4973,20 +4973,20 @@
     <row r="150">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>12IP20300</t>
+          <t>WLHSBMSQ10</t>
         </is>
       </c>
       <c r="B150" s="8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C150" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E150" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
@@ -4995,24 +4995,24 @@
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>12IP67350</t>
+          <t>12IP20300</t>
         </is>
       </c>
       <c r="B151" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C151" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E151" s="8" t="n">
         <v>16</v>
@@ -5031,17 +5031,17 @@
     <row r="152">
       <c r="A152" s="7" t="inlineStr">
         <is>
-          <t>24IP6736</t>
+          <t>CBSF100</t>
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C152" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D152" s="8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E152" s="8" t="n">
         <v>16</v>
@@ -5060,17 +5060,17 @@
     <row r="153">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>24IP6780</t>
+          <t>CCBC7</t>
         </is>
       </c>
       <c r="B153" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C153" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D153" s="8" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E153" s="8" t="n">
         <v>16</v>
@@ -5082,24 +5082,24 @@
       </c>
       <c r="G153" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>COS93BM5PK</t>
+          <t>CRSF100BM+PHHT1PBRBM2PK - Nb</t>
         </is>
       </c>
       <c r="B154" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C154" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D154" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E154" s="8" t="n">
         <v>16</v>
@@ -5111,14 +5111,14 @@
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM2PK - Nb</t>
+          <t>CRSF100BM+PHMU1PBRGS+LSDO210BG+ICST64E27</t>
         </is>
       </c>
       <c r="B155" s="8" t="n">
@@ -5147,7 +5147,7 @@
     <row r="156">
       <c r="A156" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHMU1PBRGS+LSDO210BG+ICST64E27</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290OR-JJ</t>
         </is>
       </c>
       <c r="B156" s="8" t="n">
@@ -5176,7 +5176,7 @@
     <row r="157">
       <c r="A157" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290OR-JJ</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320OR</t>
         </is>
       </c>
       <c r="B157" s="8" t="n">
@@ -5205,7 +5205,7 @@
     <row r="158">
       <c r="A158" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320OR</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320YE-DE</t>
         </is>
       </c>
       <c r="B158" s="8" t="n">
@@ -5234,17 +5234,17 @@
     <row r="159">
       <c r="A159" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320YE-DE</t>
+          <t>LDSG125LOE274</t>
         </is>
       </c>
       <c r="B159" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C159" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D159" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E159" s="8" t="n">
         <v>16</v>
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>LDSG125LOE274</t>
+          <t>LHNSE27CO</t>
         </is>
       </c>
       <c r="B160" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C160" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D160" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E160" s="8" t="n">
         <v>16</v>
@@ -5285,24 +5285,24 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>LHNSE27CO</t>
+          <t>LHTHE27SN</t>
         </is>
       </c>
       <c r="B161" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C161" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D161" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E161" s="8" t="n">
         <v>16</v>
@@ -5314,24 +5314,24 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>LHTHE27SN</t>
+          <t>WCB3BM2PK+RPR44WH2PK j</t>
         </is>
       </c>
       <c r="B162" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C162" s="8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D162" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E162" s="8" t="n">
         <v>16</v>
@@ -5343,24 +5343,24 @@
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>WCB3BM2PK+RPR44WH2PK j</t>
+          <t>WCB7WH+RPR44WH</t>
         </is>
       </c>
       <c r="B163" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C163" s="8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D163" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E163" s="8" t="n">
         <v>16</v>
@@ -5372,27 +5372,27 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="inlineStr">
         <is>
-          <t>WCB7WH+RPR44WH</t>
+          <t>12ASIP20300</t>
         </is>
       </c>
       <c r="B164" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C164" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D164" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E164" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
@@ -5401,27 +5401,27 @@
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>WJB2</t>
+          <t>12BO100</t>
         </is>
       </c>
       <c r="B165" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C165" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D165" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
@@ -5430,24 +5430,24 @@
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>12BO100</t>
+          <t>24IP20180</t>
         </is>
       </c>
       <c r="B166" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C166" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D166" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E166" s="8" t="n">
         <v>15</v>
@@ -5459,24 +5459,24 @@
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>24IP20180</t>
+          <t>24IP6760</t>
         </is>
       </c>
       <c r="B167" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C167" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D167" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E167" s="8" t="n">
         <v>15</v>
@@ -5488,24 +5488,24 @@
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
         <is>
-          <t>24IP6760</t>
+          <t>24IP6780</t>
         </is>
       </c>
       <c r="B168" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C168" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D168" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E168" s="8" t="n">
         <v>15</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
     <row r="170">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>CRFF108YB+WSSS70YB+SCRN70YB</t>
+          <t>CBSF75</t>
         </is>
       </c>
       <c r="B170" s="8" t="n">
@@ -5582,17 +5582,17 @@
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290BU-JJ</t>
+          <t>COS93BM5PK</t>
         </is>
       </c>
       <c r="B171" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="8" t="n">
         <v>15</v>
-      </c>
-      <c r="D171" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E171" s="8" t="n">
         <v>15</v>
@@ -5604,24 +5604,24 @@
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSHR135BM+LSFT220BM</t>
+          <t>CRFF108YB+WSSS70YB+SCRN70YB</t>
         </is>
       </c>
       <c r="B172" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C172" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D172" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E172" s="8" t="n">
         <v>15</v>
@@ -5633,21 +5633,21 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+PHRI1PBRYB+LSDO300YB+ICST64E27</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290BU-JJ</t>
         </is>
       </c>
       <c r="B173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" s="8" t="n">
         <v>15</v>
-      </c>
-      <c r="C173" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D173" s="8" t="n">
         <v>0</v>
@@ -5662,24 +5662,24 @@
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="inlineStr">
         <is>
-          <t>CRSF108BM+WSST70BM</t>
+          <t>CRSF100BM+WSHR135BM+LSFT220BM</t>
         </is>
       </c>
       <c r="B174" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C174" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D174" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E174" s="8" t="n">
         <v>15</v>
@@ -5691,24 +5691,24 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E2745PK</t>
+          <t>CRSF100YB+PHRI1PBRYB+LSDO300YB+ICST64E27</t>
         </is>
       </c>
       <c r="B175" s="8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C175" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D175" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E175" s="8" t="n">
         <v>15</v>
@@ -5720,24 +5720,24 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>LHC5E27WH</t>
+          <t>LDMST64E2745PK</t>
         </is>
       </c>
       <c r="B176" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C176" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D176" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E176" s="8" t="n">
         <v>15</v>
@@ -5756,17 +5756,17 @@
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>LHC5E27WH3PK</t>
+          <t>LHC5E27WH</t>
         </is>
       </c>
       <c r="B177" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="8" t="n">
         <v>13</v>
-      </c>
-      <c r="D177" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="E177" s="8" t="n">
         <v>15</v>
@@ -5778,24 +5778,24 @@
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>LSHQ180BG2PK_DE</t>
+          <t>LHC5E27WH3PK</t>
         </is>
       </c>
       <c r="B178" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C178" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D178" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E178" s="8" t="n">
         <v>15</v>
@@ -5807,24 +5807,24 @@
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>PHSH1PBRCO</t>
+          <t>LSHQ180BG2PK_DE</t>
         </is>
       </c>
       <c r="B179" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C179" s="8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D179" s="8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E179" s="8" t="n">
         <v>15</v>
@@ -5836,27 +5836,27 @@
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="inlineStr">
         <is>
-          <t>12ASIP20300</t>
+          <t>PHSH1PBRCO</t>
         </is>
       </c>
       <c r="B180" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C180" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D180" s="8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E180" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
@@ -5865,27 +5865,27 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>12IP6720</t>
+          <t>WJB2</t>
         </is>
       </c>
       <c r="B181" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C181" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D181" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
@@ -5894,24 +5894,24 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
         <is>
-          <t>CBSF100</t>
+          <t>12IP6720</t>
         </is>
       </c>
       <c r="B182" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C182" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D182" s="8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E182" s="8" t="n">
         <v>14</v>
@@ -5930,17 +5930,17 @@
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>CBSF75</t>
+          <t>COS93BM3PK</t>
         </is>
       </c>
       <c r="B183" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C183" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D183" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E183" s="8" t="n">
         <v>14</v>
@@ -5952,24 +5952,24 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>CL2RBM5PK</t>
+          <t>CRSF100BM+PHHT1PBRBM+LSHM400HE</t>
         </is>
       </c>
       <c r="B184" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C184" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D184" s="8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E184" s="8" t="n">
         <v>14</v>
@@ -5981,24 +5981,24 @@
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>COS93BM3PK</t>
+          <t>ENC7499</t>
         </is>
       </c>
       <c r="B185" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C185" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D185" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E185" s="8" t="n">
         <v>14</v>
@@ -6010,14 +6010,14 @@
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+LSHM400HE</t>
+          <t>LDMG80E2743PK</t>
         </is>
       </c>
       <c r="B186" s="8" t="n">
@@ -6046,17 +6046,17 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>ENC7499</t>
+          <t>LDMST64E2783PK</t>
         </is>
       </c>
       <c r="B187" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C187" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D187" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E187" s="8" t="n">
         <v>14</v>
@@ -6068,24 +6068,24 @@
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>LDMG80E2743PK</t>
+          <t>LDWWE279</t>
         </is>
       </c>
       <c r="B188" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C188" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D188" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E188" s="8" t="n">
         <v>14</v>
@@ -6097,24 +6097,24 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E2783PK</t>
+          <t>O2-PV99-0CIB</t>
         </is>
       </c>
       <c r="B189" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C189" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D189" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E189" s="8" t="n">
         <v>14</v>
@@ -6126,24 +6126,24 @@
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>LDWWE279</t>
+          <t>PHCD1PBRBW+LSTM310BM</t>
         </is>
       </c>
       <c r="B190" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="8" t="n">
         <v>14</v>
-      </c>
-      <c r="C190" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E190" s="8" t="n">
         <v>14</v>
@@ -6155,27 +6155,27 @@
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>O2-PV99-0CIB</t>
+          <t>24IP67100</t>
         </is>
       </c>
       <c r="B191" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C191" s="8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D191" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
@@ -6184,14 +6184,14 @@
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>PHCD1PBRBW+LSTM310BM</t>
+          <t>24IP67200</t>
         </is>
       </c>
       <c r="B192" s="8" t="n">
@@ -6201,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="D192" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E192" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
@@ -6220,17 +6220,17 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>12IP20500</t>
+          <t>24IP6724</t>
         </is>
       </c>
       <c r="B193" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C193" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D193" s="8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E193" s="8" t="n">
         <v>13</v>
@@ -6242,24 +6242,24 @@
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="inlineStr">
         <is>
-          <t>24IP67100</t>
+          <t>CCBC5</t>
         </is>
       </c>
       <c r="B194" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C194" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D194" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E194" s="8" t="n">
         <v>13</v>
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>24IP67200</t>
+          <t>CL2RBM5PK</t>
         </is>
       </c>
       <c r="B195" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C195" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D195" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E195" s="8" t="n">
         <v>13</v>
@@ -6300,24 +6300,24 @@
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>24IP6724</t>
+          <t>CL2TIV</t>
         </is>
       </c>
       <c r="B196" s="8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C196" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D196" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E196" s="8" t="n">
         <v>13</v>
@@ -6329,24 +6329,24 @@
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>CCBC5</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM-JJ</t>
         </is>
       </c>
       <c r="B197" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C197" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D197" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E197" s="8" t="n">
         <v>13</v>
@@ -6358,21 +6358,21 @@
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="inlineStr">
         <is>
-          <t>CL2TIV</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290GR-JJ</t>
         </is>
       </c>
       <c r="B198" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" s="8" t="n">
         <v>13</v>
-      </c>
-      <c r="C198" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D198" s="8" t="n">
         <v>0</v>
@@ -6387,14 +6387,14 @@
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BM-JJ</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290YE-JJ</t>
         </is>
       </c>
       <c r="B199" s="8" t="n">
@@ -6423,17 +6423,17 @@
     <row r="200">
       <c r="A200" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290GR-JJ</t>
+          <t>CRSF100BM+WSCH135BM+LSHH240BM+ICST64E27</t>
         </is>
       </c>
       <c r="B200" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C200" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D200" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E200" s="8" t="n">
         <v>13</v>
@@ -6445,14 +6445,14 @@
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290YE-JJ</t>
+          <t>CRSF100CH+PHCHPCRCH+LSMS320BT-DE</t>
         </is>
       </c>
       <c r="B201" s="8" t="n">
@@ -6481,17 +6481,17 @@
     <row r="202">
       <c r="A202" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSCH135BM+LSHH240BM+ICST64E27</t>
+          <t>CRSF120YB+WSRH230YB+LSMS320GR</t>
         </is>
       </c>
       <c r="B202" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C202" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D202" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E202" s="8" t="n">
         <v>13</v>
@@ -6503,21 +6503,21 @@
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CH+PHCHPCRCH+LSMS320BT-DE</t>
+          <t>LDMG95E2786PK</t>
         </is>
       </c>
       <c r="B203" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C203" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D203" s="8" t="n">
         <v>0</v>
@@ -6532,21 +6532,21 @@
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
         <is>
-          <t>CRSF120YB+WSRH230YB+LSMS320GR</t>
+          <t>PCBS16T10BM3PK</t>
         </is>
       </c>
       <c r="B204" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C204" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D204" s="8" t="n">
         <v>0</v>
@@ -6561,24 +6561,24 @@
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>LDMG80E2742PK</t>
+          <t>PHSH1PBRYB</t>
         </is>
       </c>
       <c r="B205" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C205" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="C205" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D205" s="8" t="n">
-        <v>10</v>
       </c>
       <c r="E205" s="8" t="n">
         <v>13</v>
@@ -6597,7 +6597,7 @@
     <row r="206">
       <c r="A206" s="7" t="inlineStr">
         <is>
-          <t>PCBS16T10BM3PK</t>
+          <t>PHSHF1PBRYB+LSSS300BM+ICST64E2740</t>
         </is>
       </c>
       <c r="B206" s="8" t="n">
@@ -6626,17 +6626,17 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>PHSH1PBRYB</t>
+          <t>WCB7BM+RPR44WH_DE</t>
         </is>
       </c>
       <c r="B207" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C207" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D207" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E207" s="8" t="n">
         <v>13</v>
@@ -6648,14 +6648,14 @@
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>PHSHF1PBRYB+LSSS300BM+ICST64E2740</t>
+          <t>WSNWBM+LSCY290BM</t>
         </is>
       </c>
       <c r="B208" s="8" t="n">
@@ -6684,20 +6684,20 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>WCB7BM+RPR44WH_DE</t>
+          <t>12BO282PK</t>
         </is>
       </c>
       <c r="B209" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C209" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D209" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E209" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
@@ -6706,27 +6706,27 @@
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
         <is>
-          <t>WSLH200BM</t>
+          <t>12IP20200</t>
         </is>
       </c>
       <c r="B210" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C210" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D210" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E210" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
@@ -6735,27 +6735,27 @@
       </c>
       <c r="G210" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>WSNWBM+LSCY290BM</t>
+          <t>12IP20500</t>
         </is>
       </c>
       <c r="B211" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C211" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D211" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E211" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
@@ -6764,24 +6764,24 @@
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>12BO282PK</t>
+          <t>BC3W50</t>
         </is>
       </c>
       <c r="B212" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C212" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D212" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E212" s="8" t="n">
         <v>12</v>
@@ -6793,24 +6793,24 @@
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>12IP20200</t>
+          <t>CCBKNWE50</t>
         </is>
       </c>
       <c r="B213" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C213" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D213" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E213" s="8" t="n">
         <v>12</v>
@@ -6822,24 +6822,24 @@
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="inlineStr">
         <is>
-          <t>BC3W50</t>
+          <t>CL3RGD</t>
         </is>
       </c>
       <c r="B214" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C214" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D214" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E214" s="8" t="n">
         <v>12</v>
@@ -6851,24 +6851,24 @@
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE50</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GR</t>
         </is>
       </c>
       <c r="B215" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C215" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D215" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E215" s="8" t="n">
         <v>12</v>
@@ -6880,24 +6880,24 @@
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="7" t="inlineStr">
         <is>
-          <t>CL3RGD</t>
+          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY-JJ</t>
         </is>
       </c>
       <c r="B216" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C216" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D216" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E216" s="8" t="n">
         <v>12</v>
@@ -6909,21 +6909,21 @@
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GR</t>
+          <t>CRSF100BM+WSAFT200BG</t>
         </is>
       </c>
       <c r="B217" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C217" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D217" s="8" t="n">
         <v>0</v>
@@ -6938,21 +6938,21 @@
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHSH1PBRBM+LSCY290GY-JJ</t>
+          <t>CRSF100WH+PHTT1PCRCH</t>
         </is>
       </c>
       <c r="B218" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C218" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D218" s="8" t="n">
         <v>0</v>
@@ -6967,24 +6967,24 @@
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSAFT200BG</t>
+          <t>CRSF108CO+WSST70CO+ICST64E2740</t>
         </is>
       </c>
       <c r="B219" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C219" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D219" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E219" s="8" t="n">
         <v>12</v>
@@ -6996,24 +6996,24 @@
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>CRSF100OR</t>
+          <t>LDMST64E278APK</t>
         </is>
       </c>
       <c r="B220" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C220" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D220" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E220" s="8" t="n">
         <v>12</v>
@@ -7025,21 +7025,21 @@
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>CRSF100WH+PHTT1PCRCH</t>
+          <t>LSCY290BC+RPR44WH G</t>
         </is>
       </c>
       <c r="B221" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C221" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="C221" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D221" s="8" t="n">
         <v>0</v>
@@ -7054,24 +7054,24 @@
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="7" t="inlineStr">
         <is>
-          <t>CRSF108CO+WSST70CO+ICST64E2740</t>
+          <t>LSCY290BD+RPR44WH</t>
         </is>
       </c>
       <c r="B222" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C222" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D222" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E222" s="8" t="n">
         <v>12</v>
@@ -7083,24 +7083,24 @@
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>LDMST64E278APK</t>
+          <t>LSDO300SN+RPR44WH</t>
         </is>
       </c>
       <c r="B223" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C223" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D223" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E223" s="8" t="n">
         <v>12</v>
@@ -7112,21 +7112,21 @@
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BC+RPR44WH G</t>
+          <t>PHCD1PBRBW+LSCY290BC</t>
         </is>
       </c>
       <c r="B224" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C224" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D224" s="8" t="n">
         <v>0</v>
@@ -7141,21 +7141,21 @@
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BD+RPR44WH</t>
+          <t>PHSHF1PBRYB+LSSS300BS+ICST64E27</t>
         </is>
       </c>
       <c r="B225" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C225" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D225" s="8" t="n">
         <v>0</v>
@@ -7170,21 +7170,21 @@
       </c>
       <c r="G225" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="inlineStr">
         <is>
-          <t>LSDO300SN+RPR44WH</t>
+          <t>PLWPBM_DE</t>
         </is>
       </c>
       <c r="B226" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C226" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="C226" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D226" s="8" t="n">
         <v>0</v>
@@ -7199,24 +7199,24 @@
       </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>PHCD1PBRBW+LSCY290BC</t>
+          <t>SPSDP2WH3PK</t>
         </is>
       </c>
       <c r="B227" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C227" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D227" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" s="8" t="n">
         <v>12</v>
@@ -7228,14 +7228,14 @@
       </c>
       <c r="G227" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify listing</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="inlineStr">
         <is>
-          <t>PHSHF1PBRYB+LSSS300BS+ICST64E27</t>
+          <t>WCCYSP160GD</t>
         </is>
       </c>
       <c r="B228" s="8" t="n">
@@ -7264,17 +7264,17 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>PLWPBM_DE</t>
+          <t>WLRPE27BM</t>
         </is>
       </c>
       <c r="B229" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C229" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" s="8" t="n">
         <v>12</v>
-      </c>
-      <c r="D229" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E229" s="8" t="n">
         <v>12</v>
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G229" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="7" t="inlineStr">
         <is>
-          <t>SPSDP2WH3PK</t>
+          <t>WSLH200BM+ICST64E27</t>
         </is>
       </c>
       <c r="B230" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C230" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D230" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E230" s="8" t="n">
         <v>12</v>
@@ -7315,27 +7315,27 @@
       </c>
       <c r="G230" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>WCCYSP160GD</t>
+          <t>5IP2028</t>
         </is>
       </c>
       <c r="B231" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C231" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D231" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E231" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F231" s="7" t="inlineStr">
         <is>
@@ -7344,27 +7344,27 @@
       </c>
       <c r="G231" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
         <is>
-          <t>WLRPE27BM</t>
+          <t>5IP2030</t>
         </is>
       </c>
       <c r="B232" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C232" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D232" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E232" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F232" s="7" t="inlineStr">
         <is>
@@ -7373,27 +7373,27 @@
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>WSLH200BM+ICST64E27</t>
+          <t>CC5/W</t>
         </is>
       </c>
       <c r="B233" s="8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C233" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D233" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E233" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
@@ -7402,24 +7402,24 @@
       </c>
       <c r="G233" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="7" t="inlineStr">
         <is>
-          <t>5IP2028</t>
+          <t>CCBC24</t>
         </is>
       </c>
       <c r="B234" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C234" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D234" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E234" s="8" t="n">
         <v>11</v>
@@ -7431,24 +7431,24 @@
       </c>
       <c r="G234" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>5IP2030</t>
+          <t>CCBKNWE7-IFR</t>
         </is>
       </c>
       <c r="B235" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C235" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D235" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E235" s="8" t="n">
         <v>11</v>
@@ -7460,24 +7460,24 @@
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="7" t="inlineStr">
         <is>
-          <t>CC5/W</t>
+          <t>CL3THE</t>
         </is>
       </c>
       <c r="B236" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C236" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="D236" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E236" s="8" t="n">
         <v>11</v>
@@ -7489,24 +7489,24 @@
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>CCBC24</t>
+          <t>COS92BM5PK</t>
         </is>
       </c>
       <c r="B237" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C237" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D237" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E237" s="8" t="n">
         <v>11</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="G237" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
         <is>
-          <t>CCBC3</t>
+          <t>CRSF100BM+LHNSE27BM+SCRN70BM+LSWD360BC</t>
         </is>
       </c>
       <c r="B238" s="8" t="n">
@@ -7554,7 +7554,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>CCBKNWE7-IFR</t>
+          <t>CRSF100BM+PHCH1BMRBM+LSCY290BI_DE</t>
         </is>
       </c>
       <c r="B239" s="8" t="n">
@@ -7583,17 +7583,17 @@
     <row r="240">
       <c r="A240" s="7" t="inlineStr">
         <is>
-          <t>CL3THE</t>
+          <t>CRSF100BM+PHCN1PBRBM</t>
         </is>
       </c>
       <c r="B240" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C240" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D240" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E240" s="8" t="n">
         <v>11</v>
@@ -7605,24 +7605,24 @@
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>COS92BM5PK</t>
+          <t>CRSF100BM+PHHT1PBRBM+ICST64E27_DE</t>
         </is>
       </c>
       <c r="B241" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C241" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D241" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E241" s="8" t="n">
         <v>11</v>
@@ -7634,24 +7634,24 @@
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+LHNSE27BM+SCRN70BM+LSWD360BC</t>
+          <t>CRSF100GY+PHCH1PWRSGY+LSSS300GY</t>
         </is>
       </c>
       <c r="B242" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C242" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D242" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E242" s="8" t="n">
         <v>11</v>
@@ -7663,24 +7663,24 @@
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCH1BMRBM+LSCY290BI_DE</t>
+          <t>CRSF100OR</t>
         </is>
       </c>
       <c r="B243" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C243" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="D243" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E243" s="8" t="n">
         <v>11</v>
@@ -7692,21 +7692,21 @@
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHCN1PBRBM</t>
+          <t>IMCWFPK L</t>
         </is>
       </c>
       <c r="B244" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" s="8" t="n">
         <v>11</v>
-      </c>
-      <c r="C244" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D244" s="8" t="n">
         <v>0</v>
@@ -7721,21 +7721,21 @@
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+PHHT1PBRBM+ICST64E27_DE</t>
+          <t>LSCY290YB+RPR44WH</t>
         </is>
       </c>
       <c r="B245" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C245" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D245" s="8" t="n">
         <v>0</v>
@@ -7750,14 +7750,14 @@
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
         <is>
-          <t>CRSF100GY+PHCH1PWRSGY+LSSS300GY</t>
+          <t>LSDO300BI+RPR44WH</t>
         </is>
       </c>
       <c r="B246" s="8" t="n">
@@ -7786,17 +7786,17 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>IMCWFPK L</t>
+          <t>PHHR1HETHE</t>
         </is>
       </c>
       <c r="B247" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C247" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D247" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E247" s="8" t="n">
         <v>11</v>
@@ -7808,21 +7808,21 @@
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="7" t="inlineStr">
         <is>
-          <t>LDMG95E2786PK</t>
+          <t>TPOSBDBM</t>
         </is>
       </c>
       <c r="B248" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C248" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D248" s="8" t="n">
         <v>0</v>
@@ -7837,14 +7837,14 @@
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create eBay listing</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>LSCY290YB+RPR44WH</t>
+          <t>WSLH200BM</t>
         </is>
       </c>
       <c r="B249" s="8" t="n">
@@ -7873,20 +7873,20 @@
     <row r="250">
       <c r="A250" s="7" t="inlineStr">
         <is>
-          <t>LSDO300BI+RPR44WH</t>
+          <t>12DE2P2A</t>
         </is>
       </c>
       <c r="B250" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C250" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D250" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E250" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
@@ -7895,18 +7895,18 @@
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>PHHR1HETHE</t>
+          <t>24IP6720</t>
         </is>
       </c>
       <c r="B251" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C251" s="8" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
         <v>10</v>
       </c>
       <c r="E251" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F251" s="7" t="inlineStr">
         <is>
@@ -7924,27 +7924,27 @@
       </c>
       <c r="G251" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="7" t="inlineStr">
         <is>
-          <t>TPOSBDBM</t>
+          <t>CCBC3</t>
         </is>
       </c>
       <c r="B252" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C252" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D252" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="E252" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F252" s="7" t="inlineStr">
         <is>
@@ -7953,24 +7953,24 @@
       </c>
       <c r="G252" s="7" t="inlineStr">
         <is>
-          <t>Create eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>12DE2P2A</t>
+          <t>CCBC7.2</t>
         </is>
       </c>
       <c r="B253" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C253" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D253" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E253" s="8" t="n">
         <v>10</v>
@@ -7982,14 +7982,14 @@
       </c>
       <c r="G253" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="7" t="inlineStr">
         <is>
-          <t>24IP6720</t>
+          <t>CL3TBR</t>
         </is>
       </c>
       <c r="B254" s="8" t="n">
@@ -8018,17 +8018,17 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>CCBC7.2</t>
+          <t>CL3TOR</t>
         </is>
       </c>
       <c r="B255" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C255" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D255" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E255" s="8" t="n">
         <v>10</v>
@@ -8040,24 +8040,24 @@
       </c>
       <c r="G255" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="7" t="inlineStr">
         <is>
-          <t>CL3TBR</t>
+          <t>CL3TRO</t>
         </is>
       </c>
       <c r="B256" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C256" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D256" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E256" s="8" t="n">
         <v>10</v>
@@ -8069,14 +8069,14 @@
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CL3TOR</t>
+          <t>CRFF108CO+WSSS70CO+SCRN70CO</t>
         </is>
       </c>
       <c r="B257" s="8" t="n">
@@ -8105,7 +8105,7 @@
     <row r="258">
       <c r="A258" s="7" t="inlineStr">
         <is>
-          <t>CL3TRO</t>
+          <t>CRSF100BM+WSCH135BM+SCRN70BM+LSTF40GB</t>
         </is>
       </c>
       <c r="B258" s="8" t="n">
@@ -8134,17 +8134,17 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>CRFF108CO+WSSS70CO+SCRN70CO</t>
+          <t>CRSF100BM+WSHR135BM+LSFT220GY</t>
         </is>
       </c>
       <c r="B259" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C259" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D259" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E259" s="8" t="n">
         <v>10</v>
@@ -8156,24 +8156,24 @@
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSCH135BM+SCRN70BM+LSTF40GB</t>
+          <t>CRSF100BM2PK</t>
         </is>
       </c>
       <c r="B260" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C260" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D260" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E260" s="8" t="n">
         <v>10</v>
@@ -8185,24 +8185,24 @@
       </c>
       <c r="G260" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM+WSHR135BM+LSFT220GY</t>
+          <t>CRSF100CO+CL3TBR+LHSHE27YB</t>
         </is>
       </c>
       <c r="B261" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C261" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D261" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E261" s="8" t="n">
         <v>10</v>
@@ -8214,24 +8214,24 @@
       </c>
       <c r="G261" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="inlineStr">
         <is>
-          <t>CRSF100BM2PK</t>
+          <t>CRSF100GB+PHHA1PBRYB+LSRP260GB</t>
         </is>
       </c>
       <c r="B262" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C262" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D262" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E262" s="8" t="n">
         <v>10</v>
@@ -8243,24 +8243,24 @@
       </c>
       <c r="G262" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>CRSF100CO+CL3TBR+LHSHE27YB</t>
+          <t>CRSF100RE+PHCH1PWRSRE+LSFT220RE</t>
         </is>
       </c>
       <c r="B263" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C263" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D263" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E263" s="8" t="n">
         <v>10</v>
@@ -8272,14 +8272,14 @@
       </c>
       <c r="G263" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="7" t="inlineStr">
         <is>
-          <t>CRSF100GB+PHHA1PBRYB+LSRP260GB</t>
+          <t>CRSF100YB+LHNSE27YB+SCRN70YB+LSCY290BS</t>
         </is>
       </c>
       <c r="B264" s="8" t="n">
@@ -8308,7 +8308,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CRSF100RE+PHCH1PWRSRE+LSFT220RE</t>
+          <t>CRSF1203WH+PHTT1PWR1WH3PK+SPSPLBM3PK</t>
         </is>
       </c>
       <c r="B265" s="8" t="n">
@@ -8337,7 +8337,7 @@
     <row r="266">
       <c r="A266" s="7" t="inlineStr">
         <is>
-          <t>CRSF100YB+LHNSE27YB+SCRN70YB+LSCY290BS</t>
+          <t>LDED105E273</t>
         </is>
       </c>
       <c r="B266" s="8" t="n">
@@ -8366,14 +8366,14 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CRSF1203WH+PHTT1PWR1WH3PK+SPSPLBM3PK</t>
+          <t>LDLIE27SR4</t>
         </is>
       </c>
       <c r="B267" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C267" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D267" s="8" t="n">
         <v>0</v>
@@ -8388,24 +8388,24 @@
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="7" t="inlineStr">
         <is>
-          <t>LDED105E273</t>
+          <t>LDMT45E2742PK</t>
         </is>
       </c>
       <c r="B268" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C268" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D268" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E268" s="8" t="n">
         <v>10</v>
@@ -8417,24 +8417,24 @@
       </c>
       <c r="G268" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>LDLIE27SR4</t>
+          <t>LDST185E2742PK</t>
         </is>
       </c>
       <c r="B269" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C269" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D269" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E269" s="8" t="n">
         <v>10</v>
@@ -8446,24 +8446,24 @@
       </c>
       <c r="G269" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="7" t="inlineStr">
         <is>
-          <t>LDMT45E2742PK</t>
+          <t>LSBLP3BCR</t>
         </is>
       </c>
       <c r="B270" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C270" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D270" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E270" s="8" t="n">
         <v>10</v>
@@ -8475,24 +8475,24 @@
       </c>
       <c r="G270" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>LDST185E2742PK</t>
+          <t>LSCY290BC+RPR44WH M2</t>
         </is>
       </c>
       <c r="B271" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C271" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D271" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E271" s="8" t="n">
         <v>10</v>
@@ -8504,21 +8504,21 @@
       </c>
       <c r="G271" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + Amazon listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="7" t="inlineStr">
         <is>
-          <t>LSBLP3BCR</t>
+          <t>LSCY290OR+RPR44WH</t>
         </is>
       </c>
       <c r="B272" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C272" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D272" s="8" t="n">
         <v>0</v>
@@ -8533,14 +8533,14 @@
       </c>
       <c r="G272" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Amazon + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>LSCY290BC+RPR44WH M2</t>
+          <t>LSLT360BC2PK+RPR44WH2PK_DE</t>
         </is>
       </c>
       <c r="B273" s="8" t="n">
@@ -8569,7 +8569,7 @@
     <row r="274">
       <c r="A274" s="7" t="inlineStr">
         <is>
-          <t>LSCY290OR+RPR44WH</t>
+          <t>PHCD1PBRBW+LSCY210BM</t>
         </is>
       </c>
       <c r="B274" s="8" t="n">
@@ -8598,7 +8598,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>LSLT360BC2PK+RPR44WH2PK_DE</t>
+          <t>PHUH1HETBM+LSHM300HE_M2</t>
         </is>
       </c>
       <c r="B275" s="8" t="n">
@@ -8627,14 +8627,14 @@
     <row r="276">
       <c r="A276" s="7" t="inlineStr">
         <is>
-          <t>PHCD1PBRBW+LSCY210BM</t>
+          <t>SFCR3PBK</t>
         </is>
       </c>
       <c r="B276" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C276" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="C276" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="D276" s="8" t="n">
         <v>0</v>
@@ -8649,24 +8649,24 @@
       </c>
       <c r="G276" s="7" t="inlineStr">
         <is>
-          <t>Create Amazon + eBay listing</t>
+          <t>Create Shopify + eBay listing</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>PHUH1HETBM+LSHM300HE_M2</t>
+          <t>WJBIP686BM2PK</t>
         </is>
       </c>
       <c r="B277" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C277" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D277" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E277" s="8" t="n">
         <v>10</v>
@@ -8678,24 +8678,24 @@
       </c>
       <c r="G277" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="7" t="inlineStr">
         <is>
-          <t>SFCR3PBK</t>
+          <t>WLGI350E27BM</t>
         </is>
       </c>
       <c r="B278" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C278" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="D278" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="E278" s="8" t="n">
         <v>10</v>
@@ -8707,85 +8707,85 @@
       </c>
       <c r="G278" s="7" t="inlineStr">
         <is>
-          <t>Create Shopify + eBay listing</t>
+          <t>Create Shopify + Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="7" t="inlineStr">
-        <is>
-          <t>WJBIP686BM2PK</t>
-        </is>
-      </c>
-      <c r="B279" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C279" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D279" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E279" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F279" s="7" t="inlineStr">
-        <is>
-          <t>Missing channel</t>
-        </is>
-      </c>
-      <c r="G279" s="7" t="inlineStr">
-        <is>
-          <t>Create Shopify + Amazon listing</t>
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>LHSHE27CO</t>
+        </is>
+      </c>
+      <c r="B279" s="10" t="n">
+        <v>169</v>
+      </c>
+      <c r="C279" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D279" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="E279" s="10" t="n">
+        <v>215</v>
+      </c>
+      <c r="F279" s="9" t="inlineStr">
+        <is>
+          <t>Shopify winner</t>
+        </is>
+      </c>
+      <c r="G279" s="9" t="inlineStr">
+        <is>
+          <t>Improve Amazon/eBay listing</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="7" t="inlineStr">
-        <is>
-          <t>WLGI350E27BM</t>
-        </is>
-      </c>
-      <c r="B280" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C280" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D280" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E280" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F280" s="7" t="inlineStr">
-        <is>
-          <t>Missing channel</t>
-        </is>
-      </c>
-      <c r="G280" s="7" t="inlineStr">
-        <is>
-          <t>Create Shopify + Amazon listing</t>
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>12BO72</t>
+        </is>
+      </c>
+      <c r="B280" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="C280" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D280" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E280" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F280" s="9" t="inlineStr">
+        <is>
+          <t>Shopify winner</t>
+        </is>
+      </c>
+      <c r="G280" s="9" t="inlineStr">
+        <is>
+          <t>Improve Amazon listing</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>LHSHE27CO</t>
+          <t>LSCY210BG+RPR44WH</t>
         </is>
       </c>
       <c r="B281" s="10" t="n">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C281" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D281" s="10" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E281" s="10" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
@@ -8794,27 +8794,27 @@
       </c>
       <c r="G281" s="9" t="inlineStr">
         <is>
-          <t>Improve Amazon listing</t>
+          <t>Improve Amazon/eBay listing</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>12BO72</t>
+          <t>CBSF120</t>
         </is>
       </c>
       <c r="B282" s="10" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C282" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D282" s="10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E282" s="10" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
@@ -8823,70 +8823,12 @@
       </c>
       <c r="G282" s="9" t="inlineStr">
         <is>
-          <t>Improve Amazon listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="9" t="inlineStr">
-        <is>
-          <t>LSCY210BG+RPR44WH</t>
-        </is>
-      </c>
-      <c r="B283" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="C283" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D283" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E283" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="F283" s="9" t="inlineStr">
-        <is>
-          <t>Shopify winner</t>
-        </is>
-      </c>
-      <c r="G283" s="9" t="inlineStr">
-        <is>
           <t>Improve Amazon/eBay listing</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="9" t="inlineStr">
-        <is>
-          <t>CBSF120</t>
-        </is>
-      </c>
-      <c r="B284" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="C284" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D284" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E284" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="F284" s="9" t="inlineStr">
-        <is>
-          <t>Shopify winner</t>
-        </is>
-      </c>
-      <c r="G284" s="9" t="inlineStr">
-        <is>
-          <t>Improve Amazon/eBay listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G284"/>
+  <autoFilter ref="A1:G282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>